--- a/catalog/product_worksheet.xlsx
+++ b/catalog/product_worksheet.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -49,6 +49,11 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE8A3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -62,12 +67,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2825,7 +2831,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>108</row>
+      <row>109</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -2850,7 +2856,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>109</row>
+      <row>110</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -2875,7 +2881,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>110</row>
+      <row>111</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -2900,7 +2906,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>111</row>
+      <row>112</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -2925,7 +2931,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>112</row>
+      <row>113</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -2950,7 +2956,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>113</row>
+      <row>114</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -2975,7 +2981,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>114</row>
+      <row>115</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3000,7 +3006,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>115</row>
+      <row>116</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3025,7 +3031,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>116</row>
+      <row>117</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3050,7 +3056,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>117</row>
+      <row>118</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3075,7 +3081,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>118</row>
+      <row>119</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3100,7 +3106,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>119</row>
+      <row>120</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3125,7 +3131,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>120</row>
+      <row>121</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3150,7 +3156,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>121</row>
+      <row>122</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3175,7 +3181,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>122</row>
+      <row>123</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3200,7 +3206,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>123</row>
+      <row>124</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3225,7 +3231,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>124</row>
+      <row>125</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3250,7 +3256,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>125</row>
+      <row>126</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3275,7 +3281,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>126</row>
+      <row>127</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3300,7 +3306,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>127</row>
+      <row>130</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3325,7 +3331,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>128</row>
+      <row>131</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3350,7 +3356,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>129</row>
+      <row>132</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3375,7 +3381,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>130</row>
+      <row>133</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3400,7 +3406,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>131</row>
+      <row>134</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3425,7 +3431,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>132</row>
+      <row>135</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3450,7 +3456,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>133</row>
+      <row>136</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3475,7 +3481,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>134</row>
+      <row>137</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3500,7 +3506,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>135</row>
+      <row>138</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3525,7 +3531,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>136</row>
+      <row>139</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3550,7 +3556,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>137</row>
+      <row>140</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3575,7 +3581,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>138</row>
+      <row>141</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3600,7 +3606,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>139</row>
+      <row>142</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3625,7 +3631,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>140</row>
+      <row>143</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3650,7 +3656,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>141</row>
+      <row>144</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3675,7 +3681,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>142</row>
+      <row>145</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3700,7 +3706,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>143</row>
+      <row>146</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3725,7 +3731,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>144</row>
+      <row>147</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3750,7 +3756,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>145</row>
+      <row>148</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3775,7 +3781,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>146</row>
+      <row>149</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3800,7 +3806,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>147</row>
+      <row>150</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3825,7 +3831,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>148</row>
+      <row>151</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3850,7 +3856,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>149</row>
+      <row>152</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3875,7 +3881,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>150</row>
+      <row>153</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3900,7 +3906,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>151</row>
+      <row>154</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3925,7 +3931,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>152</row>
+      <row>155</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3950,7 +3956,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>153</row>
+      <row>156</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -3975,7 +3981,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>154</row>
+      <row>157</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4000,7 +4006,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>155</row>
+      <row>158</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4025,7 +4031,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>156</row>
+      <row>159</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4050,7 +4056,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>157</row>
+      <row>160</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4075,7 +4081,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>158</row>
+      <row>161</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4100,7 +4106,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>159</row>
+      <row>162</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4125,7 +4131,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>160</row>
+      <row>163</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4150,7 +4156,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>161</row>
+      <row>164</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4175,7 +4181,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>162</row>
+      <row>165</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4200,7 +4206,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>163</row>
+      <row>166</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4225,7 +4231,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>164</row>
+      <row>167</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4250,7 +4256,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>165</row>
+      <row>168</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4275,7 +4281,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>166</row>
+      <row>169</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4300,7 +4306,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>167</row>
+      <row>170</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4325,7 +4331,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>168</row>
+      <row>171</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4350,7 +4356,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>169</row>
+      <row>172</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4375,7 +4381,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>170</row>
+      <row>173</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4400,7 +4406,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>171</row>
+      <row>174</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4425,7 +4431,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>172</row>
+      <row>175</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4450,7 +4456,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>173</row>
+      <row>176</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4475,7 +4481,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>174</row>
+      <row>177</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4500,7 +4506,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>175</row>
+      <row>178</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4525,7 +4531,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>176</row>
+      <row>179</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4550,7 +4556,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>177</row>
+      <row>180</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4575,7 +4581,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>178</row>
+      <row>181</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4600,7 +4606,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>179</row>
+      <row>182</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4625,7 +4631,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>180</row>
+      <row>183</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4650,7 +4656,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>181</row>
+      <row>184</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4675,7 +4681,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>182</row>
+      <row>185</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4700,7 +4706,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>183</row>
+      <row>186</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4725,7 +4731,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>184</row>
+      <row>187</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4750,7 +4756,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>185</row>
+      <row>188</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4775,7 +4781,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>186</row>
+      <row>189</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4800,7 +4806,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>187</row>
+      <row>190</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4825,7 +4831,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>188</row>
+      <row>191</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4850,7 +4856,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>189</row>
+      <row>192</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4875,7 +4881,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>190</row>
+      <row>193</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4900,7 +4906,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>191</row>
+      <row>194</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4925,7 +4931,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>192</row>
+      <row>195</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4950,7 +4956,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>193</row>
+      <row>196</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -4975,7 +4981,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>194</row>
+      <row>197</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5000,7 +5006,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>195</row>
+      <row>198</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5025,7 +5031,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>196</row>
+      <row>199</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5050,7 +5056,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>197</row>
+      <row>200</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5075,7 +5081,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>198</row>
+      <row>201</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5100,7 +5106,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>199</row>
+      <row>202</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5125,7 +5131,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>200</row>
+      <row>203</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5150,7 +5156,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>201</row>
+      <row>204</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5175,7 +5181,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>202</row>
+      <row>205</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5200,7 +5206,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>203</row>
+      <row>206</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5225,7 +5231,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>204</row>
+      <row>207</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5250,7 +5256,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>205</row>
+      <row>208</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5275,7 +5281,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>206</row>
+      <row>209</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5300,7 +5306,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>207</row>
+      <row>210</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5325,7 +5331,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>208</row>
+      <row>211</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5350,7 +5356,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>209</row>
+      <row>212</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5375,7 +5381,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>210</row>
+      <row>213</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5400,7 +5406,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>211</row>
+      <row>214</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5425,7 +5431,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>212</row>
+      <row>215</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5450,7 +5456,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>213</row>
+      <row>216</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5475,7 +5481,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>214</row>
+      <row>217</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5500,7 +5506,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>215</row>
+      <row>218</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5525,7 +5531,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>216</row>
+      <row>219</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5550,7 +5556,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>217</row>
+      <row>220</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5575,7 +5581,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>218</row>
+      <row>222</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5600,7 +5606,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>219</row>
+      <row>223</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5625,7 +5631,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>220</row>
+      <row>224</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5650,7 +5656,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>221</row>
+      <row>225</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5675,7 +5681,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>222</row>
+      <row>226</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5700,7 +5706,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>223</row>
+      <row>227</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5725,7 +5731,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>224</row>
+      <row>228</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5750,7 +5756,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>225</row>
+      <row>229</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5775,7 +5781,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>226</row>
+      <row>230</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5800,7 +5806,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>227</row>
+      <row>231</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5825,7 +5831,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>228</row>
+      <row>232</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5850,7 +5856,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>229</row>
+      <row>233</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5875,7 +5881,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>230</row>
+      <row>234</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5900,7 +5906,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>231</row>
+      <row>235</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5925,7 +5931,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>232</row>
+      <row>236</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5950,7 +5956,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>233</row>
+      <row>237</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -5975,7 +5981,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>234</row>
+      <row>238</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6000,7 +6006,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>235</row>
+      <row>239</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6025,7 +6031,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>236</row>
+      <row>240</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6050,7 +6056,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>237</row>
+      <row>241</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6075,7 +6081,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>238</row>
+      <row>242</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6100,7 +6106,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>239</row>
+      <row>243</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6125,7 +6131,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>240</row>
+      <row>244</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6150,7 +6156,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>241</row>
+      <row>245</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6175,7 +6181,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>242</row>
+      <row>246</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6200,7 +6206,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>243</row>
+      <row>247</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6225,7 +6231,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>244</row>
+      <row>248</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6250,7 +6256,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>245</row>
+      <row>249</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6275,7 +6281,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>246</row>
+      <row>250</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6300,7 +6306,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>247</row>
+      <row>251</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6325,7 +6331,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>248</row>
+      <row>252</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6350,7 +6356,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>249</row>
+      <row>253</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6375,7 +6381,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>250</row>
+      <row>254</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6400,7 +6406,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>251</row>
+      <row>255</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6425,7 +6431,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>252</row>
+      <row>256</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6450,7 +6456,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>253</row>
+      <row>257</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6475,7 +6481,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>254</row>
+      <row>258</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6500,7 +6506,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>255</row>
+      <row>259</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6525,7 +6531,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>256</row>
+      <row>260</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6550,7 +6556,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>257</row>
+      <row>261</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6575,7 +6581,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>258</row>
+      <row>262</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6600,7 +6606,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>259</row>
+      <row>263</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6625,7 +6631,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>260</row>
+      <row>264</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6650,7 +6656,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>261</row>
+      <row>265</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6675,7 +6681,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>262</row>
+      <row>266</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6700,7 +6706,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>263</row>
+      <row>267</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6725,7 +6731,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>264</row>
+      <row>268</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6750,7 +6756,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>265</row>
+      <row>269</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6775,7 +6781,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>266</row>
+      <row>270</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6800,7 +6806,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>267</row>
+      <row>271</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6825,7 +6831,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>268</row>
+      <row>272</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6850,7 +6856,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>269</row>
+      <row>273</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6875,7 +6881,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>270</row>
+      <row>274</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6900,7 +6906,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>271</row>
+      <row>275</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6925,7 +6931,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>272</row>
+      <row>276</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6950,7 +6956,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>273</row>
+      <row>277</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -6975,7 +6981,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>274</row>
+      <row>278</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7000,7 +7006,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>275</row>
+      <row>279</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7025,7 +7031,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>276</row>
+      <row>280</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7050,7 +7056,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>277</row>
+      <row>281</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7075,7 +7081,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>278</row>
+      <row>282</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7100,7 +7106,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>279</row>
+      <row>283</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7125,7 +7131,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>280</row>
+      <row>284</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7150,7 +7156,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>281</row>
+      <row>285</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7175,7 +7181,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>282</row>
+      <row>286</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7200,7 +7206,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>283</row>
+      <row>287</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7225,7 +7231,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>284</row>
+      <row>288</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7250,7 +7256,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>285</row>
+      <row>289</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7275,7 +7281,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>286</row>
+      <row>290</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7300,7 +7306,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>287</row>
+      <row>291</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7325,7 +7331,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>288</row>
+      <row>292</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7350,7 +7356,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>289</row>
+      <row>293</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7375,7 +7381,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>290</row>
+      <row>294</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7400,7 +7406,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>291</row>
+      <row>295</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7425,7 +7431,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>292</row>
+      <row>296</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7450,7 +7456,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>293</row>
+      <row>297</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7475,7 +7481,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>294</row>
+      <row>298</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7500,7 +7506,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>295</row>
+      <row>299</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7525,7 +7531,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>296</row>
+      <row>300</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7550,7 +7556,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>297</row>
+      <row>301</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7575,7 +7581,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>298</row>
+      <row>302</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7600,7 +7606,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>299</row>
+      <row>303</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7625,7 +7631,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>300</row>
+      <row>304</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7650,7 +7656,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>301</row>
+      <row>305</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7675,7 +7681,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>302</row>
+      <row>306</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7700,7 +7706,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>303</row>
+      <row>307</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7725,7 +7731,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>304</row>
+      <row>308</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7750,7 +7756,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>305</row>
+      <row>309</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7775,7 +7781,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>306</row>
+      <row>310</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7800,7 +7806,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>307</row>
+      <row>311</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7825,7 +7831,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>308</row>
+      <row>312</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7850,7 +7856,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>309</row>
+      <row>313</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7875,7 +7881,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>310</row>
+      <row>314</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7900,7 +7906,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>311</row>
+      <row>315</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7925,7 +7931,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>312</row>
+      <row>316</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7950,7 +7956,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>313</row>
+      <row>317</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -7975,7 +7981,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>314</row>
+      <row>318</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8000,7 +8006,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>315</row>
+      <row>319</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8025,7 +8031,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>316</row>
+      <row>320</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8050,7 +8056,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>317</row>
+      <row>321</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8075,7 +8081,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>318</row>
+      <row>322</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8100,7 +8106,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>319</row>
+      <row>323</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8125,7 +8131,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>320</row>
+      <row>324</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8150,7 +8156,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>321</row>
+      <row>325</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8175,7 +8181,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>322</row>
+      <row>326</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8200,7 +8206,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>323</row>
+      <row>327</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8225,7 +8231,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>324</row>
+      <row>328</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8250,7 +8256,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>325</row>
+      <row>329</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8275,7 +8281,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>326</row>
+      <row>330</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8300,7 +8306,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>327</row>
+      <row>331</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8325,7 +8331,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>328</row>
+      <row>332</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8350,7 +8356,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>329</row>
+      <row>333</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8375,7 +8381,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>330</row>
+      <row>334</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8400,7 +8406,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>331</row>
+      <row>335</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8425,7 +8431,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>332</row>
+      <row>336</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8450,7 +8456,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>333</row>
+      <row>337</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8475,7 +8481,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>334</row>
+      <row>338</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8500,7 +8506,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>335</row>
+      <row>339</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8525,7 +8531,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>336</row>
+      <row>340</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8550,7 +8556,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>337</row>
+      <row>341</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8575,7 +8581,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>338</row>
+      <row>342</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8600,7 +8606,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>339</row>
+      <row>343</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8625,7 +8631,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>340</row>
+      <row>344</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8650,7 +8656,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>341</row>
+      <row>345</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8675,7 +8681,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>342</row>
+      <row>346</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8700,7 +8706,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>343</row>
+      <row>347</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8725,7 +8731,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>344</row>
+      <row>348</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8750,7 +8756,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>345</row>
+      <row>349</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8775,7 +8781,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>346</row>
+      <row>350</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8800,7 +8806,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>347</row>
+      <row>351</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8825,7 +8831,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>348</row>
+      <row>352</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8850,7 +8856,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>349</row>
+      <row>353</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8875,7 +8881,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>350</row>
+      <row>354</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8900,7 +8906,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>351</row>
+      <row>355</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8925,7 +8931,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>352</row>
+      <row>356</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8950,7 +8956,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>353</row>
+      <row>357</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -8975,7 +8981,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>354</row>
+      <row>358</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9000,7 +9006,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>355</row>
+      <row>359</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9025,7 +9031,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>356</row>
+      <row>360</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9050,7 +9056,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>357</row>
+      <row>361</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9075,7 +9081,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>358</row>
+      <row>362</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9100,7 +9106,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>359</row>
+      <row>363</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9125,7 +9131,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>360</row>
+      <row>364</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9150,7 +9156,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>361</row>
+      <row>365</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9175,7 +9181,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>362</row>
+      <row>366</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9200,7 +9206,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>363</row>
+      <row>367</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9225,7 +9231,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>364</row>
+      <row>368</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9250,7 +9256,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>365</row>
+      <row>369</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9275,7 +9281,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>366</row>
+      <row>370</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9300,7 +9306,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>367</row>
+      <row>371</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9325,7 +9331,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>368</row>
+      <row>372</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9350,7 +9356,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>369</row>
+      <row>373</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9375,7 +9381,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>370</row>
+      <row>374</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9400,7 +9406,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>371</row>
+      <row>375</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9425,7 +9431,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>372</row>
+      <row>376</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9450,7 +9456,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>373</row>
+      <row>377</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9475,7 +9481,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>374</row>
+      <row>378</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9500,7 +9506,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>375</row>
+      <row>379</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9525,7 +9531,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>376</row>
+      <row>380</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9550,7 +9556,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>377</row>
+      <row>381</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9575,7 +9581,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>378</row>
+      <row>382</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9600,7 +9606,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>379</row>
+      <row>383</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9625,7 +9631,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>380</row>
+      <row>384</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9650,7 +9656,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>381</row>
+      <row>385</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9675,7 +9681,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>382</row>
+      <row>386</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9700,7 +9706,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>383</row>
+      <row>387</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9725,7 +9731,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>384</row>
+      <row>388</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9750,7 +9756,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>385</row>
+      <row>389</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9775,7 +9781,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>386</row>
+      <row>390</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9800,7 +9806,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>387</row>
+      <row>391</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9825,7 +9831,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>388</row>
+      <row>392</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9850,7 +9856,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>389</row>
+      <row>393</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9875,7 +9881,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>390</row>
+      <row>394</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9900,7 +9906,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>391</row>
+      <row>395</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9925,7 +9931,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>392</row>
+      <row>396</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9950,7 +9956,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>393</row>
+      <row>397</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -9975,7 +9981,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>394</row>
+      <row>398</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10000,7 +10006,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>395</row>
+      <row>399</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10025,7 +10031,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>396</row>
+      <row>400</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10050,7 +10056,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>397</row>
+      <row>401</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10075,7 +10081,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>398</row>
+      <row>402</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10100,7 +10106,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>399</row>
+      <row>403</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10125,7 +10131,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>400</row>
+      <row>404</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10150,7 +10156,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>401</row>
+      <row>405</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10175,7 +10181,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>402</row>
+      <row>406</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10200,7 +10206,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>403</row>
+      <row>407</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10225,7 +10231,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>404</row>
+      <row>408</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10250,7 +10256,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>405</row>
+      <row>409</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10275,7 +10281,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>406</row>
+      <row>410</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10300,7 +10306,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>407</row>
+      <row>411</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10325,7 +10331,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>408</row>
+      <row>412</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10350,7 +10356,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>409</row>
+      <row>413</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10375,7 +10381,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>410</row>
+      <row>414</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10400,7 +10406,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>411</row>
+      <row>415</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10425,7 +10431,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>412</row>
+      <row>416</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10450,7 +10456,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>413</row>
+      <row>417</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10475,7 +10481,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>414</row>
+      <row>418</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10500,7 +10506,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>415</row>
+      <row>419</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10525,7 +10531,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>416</row>
+      <row>420</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10550,7 +10556,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>417</row>
+      <row>421</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10575,7 +10581,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>418</row>
+      <row>422</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10600,7 +10606,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>419</row>
+      <row>423</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10625,7 +10631,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>420</row>
+      <row>424</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10650,7 +10656,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>421</row>
+      <row>425</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10675,7 +10681,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>422</row>
+      <row>426</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10700,7 +10706,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>423</row>
+      <row>427</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10725,7 +10731,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>424</row>
+      <row>428</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10750,7 +10756,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>425</row>
+      <row>429</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10775,7 +10781,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>426</row>
+      <row>430</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10800,7 +10806,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>427</row>
+      <row>431</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10825,7 +10831,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>428</row>
+      <row>432</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10850,7 +10856,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>429</row>
+      <row>433</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10875,7 +10881,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>430</row>
+      <row>434</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10900,7 +10906,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>431</row>
+      <row>435</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10925,7 +10931,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>432</row>
+      <row>436</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10950,7 +10956,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>433</row>
+      <row>439</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -10975,7 +10981,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>434</row>
+      <row>440</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11000,7 +11006,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>435</row>
+      <row>441</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11025,7 +11031,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>436</row>
+      <row>442</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11050,7 +11056,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>437</row>
+      <row>443</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11075,7 +11081,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>438</row>
+      <row>444</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11100,7 +11106,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>439</row>
+      <row>445</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11125,7 +11131,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>440</row>
+      <row>446</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11150,7 +11156,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>441</row>
+      <row>447</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11175,7 +11181,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>442</row>
+      <row>448</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11200,7 +11206,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>443</row>
+      <row>449</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11225,7 +11231,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>444</row>
+      <row>450</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11250,7 +11256,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>445</row>
+      <row>451</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11275,7 +11281,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>446</row>
+      <row>452</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11300,7 +11306,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>447</row>
+      <row>453</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11325,7 +11331,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>448</row>
+      <row>454</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11350,7 +11356,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>449</row>
+      <row>455</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11375,7 +11381,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>450</row>
+      <row>456</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11400,7 +11406,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>451</row>
+      <row>457</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11425,7 +11431,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>452</row>
+      <row>458</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11450,7 +11456,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>453</row>
+      <row>459</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11475,7 +11481,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>454</row>
+      <row>460</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11500,7 +11506,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>455</row>
+      <row>461</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11525,7 +11531,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>456</row>
+      <row>462</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11550,7 +11556,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>457</row>
+      <row>463</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11575,7 +11581,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>458</row>
+      <row>464</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11600,7 +11606,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>459</row>
+      <row>465</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11625,7 +11631,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>460</row>
+      <row>466</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11650,7 +11656,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>461</row>
+      <row>467</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11675,7 +11681,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>462</row>
+      <row>468</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11700,7 +11706,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>463</row>
+      <row>469</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11725,7 +11731,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>464</row>
+      <row>470</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11750,7 +11756,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>465</row>
+      <row>471</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11775,7 +11781,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>466</row>
+      <row>472</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11800,7 +11806,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>467</row>
+      <row>473</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11825,7 +11831,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>468</row>
+      <row>474</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11850,7 +11856,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>469</row>
+      <row>475</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11875,7 +11881,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>470</row>
+      <row>476</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11900,7 +11906,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>471</row>
+      <row>477</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11925,7 +11931,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>472</row>
+      <row>478</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11950,7 +11956,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>473</row>
+      <row>479</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -11975,7 +11981,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>474</row>
+      <row>480</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12000,7 +12006,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>475</row>
+      <row>481</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12025,7 +12031,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>476</row>
+      <row>482</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12050,7 +12056,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>477</row>
+      <row>483</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12075,7 +12081,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>478</row>
+      <row>484</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12100,7 +12106,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>479</row>
+      <row>485</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12125,7 +12131,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>480</row>
+      <row>486</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12150,7 +12156,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>481</row>
+      <row>487</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12175,7 +12181,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>482</row>
+      <row>488</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12200,7 +12206,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>483</row>
+      <row>489</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12225,7 +12231,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>484</row>
+      <row>490</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12250,7 +12256,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>485</row>
+      <row>491</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12275,7 +12281,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>486</row>
+      <row>492</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12300,7 +12306,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>487</row>
+      <row>493</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12325,7 +12331,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>488</row>
+      <row>494</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12350,7 +12356,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>489</row>
+      <row>495</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12375,7 +12381,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>490</row>
+      <row>496</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12400,7 +12406,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>491</row>
+      <row>497</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12425,7 +12431,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>492</row>
+      <row>498</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12450,7 +12456,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>493</row>
+      <row>499</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12475,7 +12481,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>494</row>
+      <row>500</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12500,7 +12506,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>495</row>
+      <row>501</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12525,7 +12531,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>496</row>
+      <row>502</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12550,7 +12556,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>497</row>
+      <row>503</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12575,7 +12581,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>498</row>
+      <row>504</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12600,7 +12606,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>499</row>
+      <row>505</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12625,7 +12631,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>500</row>
+      <row>506</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12650,7 +12656,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>501</row>
+      <row>507</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12675,7 +12681,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>502</row>
+      <row>508</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12700,7 +12706,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>503</row>
+      <row>509</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12725,7 +12731,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>504</row>
+      <row>510</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12750,7 +12756,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>505</row>
+      <row>511</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12775,7 +12781,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>506</row>
+      <row>512</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12800,7 +12806,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>507</row>
+      <row>513</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12825,7 +12831,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>508</row>
+      <row>514</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12850,7 +12856,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>509</row>
+      <row>515</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12875,7 +12881,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>510</row>
+      <row>516</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12900,7 +12906,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>511</row>
+      <row>517</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12925,7 +12931,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>512</row>
+      <row>518</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12950,7 +12956,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>513</row>
+      <row>519</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -12975,7 +12981,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>514</row>
+      <row>520</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13000,7 +13006,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>515</row>
+      <row>521</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13025,7 +13031,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>516</row>
+      <row>522</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13050,7 +13056,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>517</row>
+      <row>523</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13075,7 +13081,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>518</row>
+      <row>524</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13100,7 +13106,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>519</row>
+      <row>525</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13125,7 +13131,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>520</row>
+      <row>526</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13150,7 +13156,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>521</row>
+      <row>527</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13175,7 +13181,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>522</row>
+      <row>528</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13200,7 +13206,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>523</row>
+      <row>529</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13225,7 +13231,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>524</row>
+      <row>530</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13250,7 +13256,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>525</row>
+      <row>531</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13275,7 +13281,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>526</row>
+      <row>532</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13300,7 +13306,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>527</row>
+      <row>533</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13325,7 +13331,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>528</row>
+      <row>534</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13350,7 +13356,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>529</row>
+      <row>535</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13375,7 +13381,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>530</row>
+      <row>536</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13400,7 +13406,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>531</row>
+      <row>537</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13425,7 +13431,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>532</row>
+      <row>538</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13450,7 +13456,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>533</row>
+      <row>539</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13475,7 +13481,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>534</row>
+      <row>540</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13500,7 +13506,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>535</row>
+      <row>541</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13525,7 +13531,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>536</row>
+      <row>542</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13550,7 +13556,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>537</row>
+      <row>543</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13575,7 +13581,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>538</row>
+      <row>544</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13600,7 +13606,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>539</row>
+      <row>545</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13625,7 +13631,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>540</row>
+      <row>546</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13650,7 +13656,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>541</row>
+      <row>547</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13675,7 +13681,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>542</row>
+      <row>548</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13700,7 +13706,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>543</row>
+      <row>549</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13725,7 +13731,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>544</row>
+      <row>550</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13750,7 +13756,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>545</row>
+      <row>551</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13775,7 +13781,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>546</row>
+      <row>552</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13800,7 +13806,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>547</row>
+      <row>553</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13825,7 +13831,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>548</row>
+      <row>554</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13850,7 +13856,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>549</row>
+      <row>555</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13875,7 +13881,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>550</row>
+      <row>556</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13900,7 +13906,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>551</row>
+      <row>557</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13925,7 +13931,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>552</row>
+      <row>558</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13950,7 +13956,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>553</row>
+      <row>559</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -13975,7 +13981,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>554</row>
+      <row>560</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14000,7 +14006,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>555</row>
+      <row>561</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14025,7 +14031,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>556</row>
+      <row>562</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14050,7 +14056,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>557</row>
+      <row>563</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14075,7 +14081,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>558</row>
+      <row>564</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14100,7 +14106,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>559</row>
+      <row>565</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14125,7 +14131,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>560</row>
+      <row>566</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14150,7 +14156,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>561</row>
+      <row>567</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14175,7 +14181,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>562</row>
+      <row>568</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14200,7 +14206,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>563</row>
+      <row>569</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14225,7 +14231,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>564</row>
+      <row>570</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14250,7 +14256,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>565</row>
+      <row>571</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14275,7 +14281,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>566</row>
+      <row>572</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14300,7 +14306,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>567</row>
+      <row>574</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14325,7 +14331,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>568</row>
+      <row>575</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14350,7 +14356,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>569</row>
+      <row>576</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14375,7 +14381,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>570</row>
+      <row>577</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14400,7 +14406,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>571</row>
+      <row>578</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14425,7 +14431,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>572</row>
+      <row>579</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14450,7 +14456,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>573</row>
+      <row>580</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14475,7 +14481,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>574</row>
+      <row>581</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14500,7 +14506,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>575</row>
+      <row>582</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14525,7 +14531,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>576</row>
+      <row>583</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14550,7 +14556,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>577</row>
+      <row>584</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14575,7 +14581,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>578</row>
+      <row>585</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14600,7 +14606,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>579</row>
+      <row>586</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14625,7 +14631,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>580</row>
+      <row>587</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14650,7 +14656,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>581</row>
+      <row>588</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14675,7 +14681,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>582</row>
+      <row>589</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14700,7 +14706,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>583</row>
+      <row>590</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14725,7 +14731,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>584</row>
+      <row>591</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14750,7 +14756,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>585</row>
+      <row>592</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14775,7 +14781,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>586</row>
+      <row>593</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14800,7 +14806,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>587</row>
+      <row>594</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14825,7 +14831,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>588</row>
+      <row>595</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14850,7 +14856,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>589</row>
+      <row>596</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14875,7 +14881,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>590</row>
+      <row>597</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14900,7 +14906,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>591</row>
+      <row>598</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14925,7 +14931,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>592</row>
+      <row>599</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14950,7 +14956,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>593</row>
+      <row>600</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -14975,7 +14981,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>594</row>
+      <row>601</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15000,7 +15006,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>595</row>
+      <row>602</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15025,7 +15031,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>596</row>
+      <row>603</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15050,7 +15056,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>597</row>
+      <row>604</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15075,7 +15081,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>598</row>
+      <row>605</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15100,7 +15106,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>599</row>
+      <row>606</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15125,7 +15131,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>600</row>
+      <row>607</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15150,7 +15156,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>601</row>
+      <row>608</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15175,7 +15181,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>602</row>
+      <row>609</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15200,7 +15206,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>603</row>
+      <row>610</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15225,7 +15231,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>604</row>
+      <row>611</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15250,7 +15256,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>605</row>
+      <row>612</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15275,7 +15281,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>606</row>
+      <row>613</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15300,7 +15306,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>607</row>
+      <row>614</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15325,7 +15331,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>608</row>
+      <row>616</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15350,7 +15356,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>609</row>
+      <row>617</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15375,7 +15381,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>610</row>
+      <row>618</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15400,7 +15406,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>611</row>
+      <row>619</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15425,7 +15431,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>612</row>
+      <row>620</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15450,7 +15456,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>613</row>
+      <row>621</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15475,7 +15481,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>614</row>
+      <row>622</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15500,7 +15506,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>615</row>
+      <row>623</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15525,7 +15531,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>616</row>
+      <row>624</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15550,7 +15556,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>617</row>
+      <row>625</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15575,7 +15581,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>618</row>
+      <row>626</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15600,7 +15606,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>619</row>
+      <row>627</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15625,7 +15631,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>620</row>
+      <row>628</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15650,7 +15656,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>621</row>
+      <row>629</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15675,7 +15681,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>622</row>
+      <row>630</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15700,7 +15706,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>623</row>
+      <row>631</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15725,7 +15731,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>624</row>
+      <row>632</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15750,7 +15756,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>625</row>
+      <row>633</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15775,7 +15781,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>626</row>
+      <row>634</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15800,7 +15806,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>627</row>
+      <row>635</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15825,7 +15831,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>628</row>
+      <row>636</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15850,7 +15856,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>629</row>
+      <row>637</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15875,7 +15881,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>630</row>
+      <row>638</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15900,7 +15906,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>631</row>
+      <row>639</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15925,7 +15931,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>632</row>
+      <row>640</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15950,7 +15956,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>633</row>
+      <row>641</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -15975,7 +15981,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>634</row>
+      <row>642</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16000,7 +16006,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>635</row>
+      <row>643</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16025,7 +16031,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>636</row>
+      <row>644</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16050,7 +16056,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>637</row>
+      <row>645</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16075,7 +16081,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>638</row>
+      <row>646</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16100,7 +16106,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>639</row>
+      <row>647</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16125,7 +16131,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>640</row>
+      <row>648</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16150,7 +16156,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>641</row>
+      <row>649</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16175,7 +16181,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>642</row>
+      <row>650</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16200,7 +16206,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>643</row>
+      <row>651</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16225,7 +16231,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>644</row>
+      <row>652</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16250,7 +16256,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>645</row>
+      <row>653</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16275,7 +16281,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>646</row>
+      <row>654</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16300,7 +16306,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>647</row>
+      <row>655</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16325,7 +16331,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>648</row>
+      <row>656</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16350,7 +16356,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>649</row>
+      <row>657</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16375,7 +16381,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>650</row>
+      <row>658</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16400,7 +16406,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>651</row>
+      <row>659</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16425,7 +16431,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>652</row>
+      <row>660</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16450,7 +16456,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>653</row>
+      <row>661</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16475,7 +16481,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>654</row>
+      <row>662</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16500,7 +16506,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>655</row>
+      <row>663</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16525,7 +16531,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>656</row>
+      <row>664</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16550,7 +16556,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>657</row>
+      <row>665</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16575,7 +16581,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>658</row>
+      <row>666</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16600,7 +16606,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>659</row>
+      <row>667</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16625,7 +16631,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>660</row>
+      <row>668</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16650,7 +16656,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>661</row>
+      <row>669</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16675,7 +16681,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>662</row>
+      <row>670</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16700,7 +16706,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>663</row>
+      <row>671</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16725,7 +16731,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>664</row>
+      <row>672</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16750,7 +16756,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>665</row>
+      <row>673</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16775,7 +16781,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>666</row>
+      <row>674</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16800,7 +16806,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>667</row>
+      <row>675</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16825,7 +16831,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>668</row>
+      <row>676</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16850,7 +16856,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>669</row>
+      <row>677</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16875,7 +16881,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>670</row>
+      <row>678</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16900,7 +16906,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>671</row>
+      <row>679</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16925,7 +16931,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>672</row>
+      <row>680</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16950,7 +16956,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>673</row>
+      <row>681</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -16975,7 +16981,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>674</row>
+      <row>682</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17000,7 +17006,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>675</row>
+      <row>683</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17025,7 +17031,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>676</row>
+      <row>684</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17050,7 +17056,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>677</row>
+      <row>685</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17075,7 +17081,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>678</row>
+      <row>686</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17100,7 +17106,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>679</row>
+      <row>687</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17125,7 +17131,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>680</row>
+      <row>688</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17150,7 +17156,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>681</row>
+      <row>689</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17175,7 +17181,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>682</row>
+      <row>690</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17200,7 +17206,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>683</row>
+      <row>691</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17225,7 +17231,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>684</row>
+      <row>692</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17250,7 +17256,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>685</row>
+      <row>693</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17275,7 +17281,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>686</row>
+      <row>694</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17300,7 +17306,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>687</row>
+      <row>695</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17325,7 +17331,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>688</row>
+      <row>696</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17350,7 +17356,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>689</row>
+      <row>697</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17375,7 +17381,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>690</row>
+      <row>698</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17400,7 +17406,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>691</row>
+      <row>699</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17425,7 +17431,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>692</row>
+      <row>700</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17450,7 +17456,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>693</row>
+      <row>701</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17475,7 +17481,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>694</row>
+      <row>702</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17500,7 +17506,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>695</row>
+      <row>703</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17525,7 +17531,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>696</row>
+      <row>704</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17550,7 +17556,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>697</row>
+      <row>705</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17575,7 +17581,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>698</row>
+      <row>706</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17600,7 +17606,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>699</row>
+      <row>707</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17625,7 +17631,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>700</row>
+      <row>708</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17650,7 +17656,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>701</row>
+      <row>709</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17675,7 +17681,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>702</row>
+      <row>710</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17700,7 +17706,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>703</row>
+      <row>711</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17725,7 +17731,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>704</row>
+      <row>712</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17750,7 +17756,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>705</row>
+      <row>713</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17775,7 +17781,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>706</row>
+      <row>714</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17800,7 +17806,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>707</row>
+      <row>715</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17825,7 +17831,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>708</row>
+      <row>716</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17850,7 +17856,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>709</row>
+      <row>717</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17875,7 +17881,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>710</row>
+      <row>718</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17900,7 +17906,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>711</row>
+      <row>719</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17925,7 +17931,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>712</row>
+      <row>720</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17950,7 +17956,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>713</row>
+      <row>721</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -17975,7 +17981,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>714</row>
+      <row>722</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18000,7 +18006,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>715</row>
+      <row>723</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18025,7 +18031,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>716</row>
+      <row>724</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18050,7 +18056,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>717</row>
+      <row>725</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18075,7 +18081,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>718</row>
+      <row>726</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18100,7 +18106,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>719</row>
+      <row>727</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18125,7 +18131,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>720</row>
+      <row>728</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18150,7 +18156,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>721</row>
+      <row>729</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18175,7 +18181,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>722</row>
+      <row>730</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18200,7 +18206,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>723</row>
+      <row>731</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18225,7 +18231,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>724</row>
+      <row>732</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18250,7 +18256,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>725</row>
+      <row>733</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18275,7 +18281,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>726</row>
+      <row>734</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18300,7 +18306,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>727</row>
+      <row>735</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18325,7 +18331,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>728</row>
+      <row>736</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18350,7 +18356,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>729</row>
+      <row>737</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18375,7 +18381,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>730</row>
+      <row>738</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18400,7 +18406,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>731</row>
+      <row>739</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18425,7 +18431,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>732</row>
+      <row>740</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18450,7 +18456,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>733</row>
+      <row>741</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18475,7 +18481,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>734</row>
+      <row>742</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18500,7 +18506,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>735</row>
+      <row>743</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18525,7 +18531,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>736</row>
+      <row>744</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18550,7 +18556,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>737</row>
+      <row>745</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18575,7 +18581,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>738</row>
+      <row>746</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18600,7 +18606,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>739</row>
+      <row>747</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18625,7 +18631,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>740</row>
+      <row>748</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18650,7 +18656,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>741</row>
+      <row>749</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18675,7 +18681,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>742</row>
+      <row>750</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18700,7 +18706,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>743</row>
+      <row>751</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18725,7 +18731,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>744</row>
+      <row>752</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18750,7 +18756,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>745</row>
+      <row>753</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18775,7 +18781,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>746</row>
+      <row>754</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18800,7 +18806,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>747</row>
+      <row>755</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18825,7 +18831,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>748</row>
+      <row>756</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18850,7 +18856,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>749</row>
+      <row>757</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18875,7 +18881,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>750</row>
+      <row>758</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18900,7 +18906,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>751</row>
+      <row>759</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18925,7 +18931,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>752</row>
+      <row>760</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18950,7 +18956,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>753</row>
+      <row>761</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -18975,7 +18981,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>754</row>
+      <row>762</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19000,7 +19006,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>755</row>
+      <row>763</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19025,7 +19031,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>756</row>
+      <row>764</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19050,7 +19056,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>757</row>
+      <row>765</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19075,7 +19081,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>758</row>
+      <row>766</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19100,7 +19106,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>759</row>
+      <row>767</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19125,7 +19131,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>760</row>
+      <row>768</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19150,7 +19156,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>761</row>
+      <row>769</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19175,7 +19181,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>762</row>
+      <row>770</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19200,7 +19206,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>763</row>
+      <row>771</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19225,7 +19231,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>764</row>
+      <row>772</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19250,7 +19256,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>765</row>
+      <row>773</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19275,7 +19281,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>766</row>
+      <row>774</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19300,7 +19306,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>767</row>
+      <row>775</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19325,7 +19331,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>768</row>
+      <row>776</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19350,7 +19356,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>769</row>
+      <row>777</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19375,7 +19381,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>770</row>
+      <row>778</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19400,7 +19406,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>771</row>
+      <row>779</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19425,7 +19431,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>772</row>
+      <row>780</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19450,7 +19456,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>773</row>
+      <row>781</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19475,7 +19481,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>774</row>
+      <row>782</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19500,7 +19506,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>775</row>
+      <row>783</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19525,7 +19531,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>776</row>
+      <row>784</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19550,7 +19556,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>777</row>
+      <row>785</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19575,7 +19581,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>778</row>
+      <row>786</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19600,7 +19606,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>779</row>
+      <row>787</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19625,7 +19631,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>780</row>
+      <row>788</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19650,7 +19656,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>781</row>
+      <row>789</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19675,7 +19681,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>782</row>
+      <row>790</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19700,7 +19706,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>783</row>
+      <row>791</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19725,7 +19731,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>784</row>
+      <row>792</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19750,7 +19756,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>785</row>
+      <row>793</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19775,7 +19781,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>786</row>
+      <row>794</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19800,7 +19806,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>787</row>
+      <row>795</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19825,7 +19831,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>788</row>
+      <row>796</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19850,7 +19856,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>789</row>
+      <row>797</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19875,7 +19881,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>790</row>
+      <row>798</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19900,7 +19906,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>791</row>
+      <row>799</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19925,7 +19931,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>792</row>
+      <row>800</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19950,7 +19956,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>793</row>
+      <row>801</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -19975,7 +19981,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>794</row>
+      <row>802</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20000,7 +20006,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>795</row>
+      <row>803</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20025,7 +20031,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>796</row>
+      <row>804</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20050,7 +20056,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>797</row>
+      <row>805</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20075,7 +20081,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>798</row>
+      <row>806</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20100,7 +20106,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>799</row>
+      <row>807</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20125,7 +20131,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>800</row>
+      <row>808</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20150,7 +20156,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>801</row>
+      <row>809</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20175,7 +20181,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>802</row>
+      <row>810</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20200,7 +20206,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>803</row>
+      <row>811</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20225,7 +20231,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>804</row>
+      <row>812</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20250,7 +20256,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>805</row>
+      <row>813</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20275,7 +20281,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>806</row>
+      <row>814</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20300,7 +20306,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>807</row>
+      <row>815</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20325,7 +20331,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>808</row>
+      <row>816</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20350,7 +20356,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>809</row>
+      <row>817</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20375,7 +20381,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>810</row>
+      <row>818</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20400,7 +20406,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>811</row>
+      <row>819</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20425,7 +20431,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>812</row>
+      <row>820</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20450,7 +20456,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>813</row>
+      <row>821</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20475,7 +20481,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>814</row>
+      <row>822</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20500,7 +20506,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>815</row>
+      <row>823</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20525,7 +20531,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>816</row>
+      <row>824</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20550,7 +20556,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>817</row>
+      <row>825</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20575,7 +20581,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>818</row>
+      <row>826</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20600,7 +20606,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>819</row>
+      <row>827</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20625,7 +20631,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>820</row>
+      <row>828</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20650,7 +20656,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>821</row>
+      <row>829</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="571500" cy="571500"/>
@@ -20661,206 +20667,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId821"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>822</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="571500" cy="571500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="822" name="Image 822" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId822"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>823</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="571500" cy="571500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="823" name="Image 823" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId823"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>824</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="571500" cy="571500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="824" name="Image 824" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId824"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>825</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="571500" cy="571500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="825" name="Image 825" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId825"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>826</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="571500" cy="571500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="826" name="Image 826" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId826"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>827</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="571500" cy="571500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="827" name="Image 827" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId827"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>828</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="571500" cy="571500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="828" name="Image 828" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId828"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>829</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="571500" cy="571500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="829" name="Image 829" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId829"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -21168,7 +20974,7 @@
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -21909,6 +21715,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n"/>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 03013-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="46.8" customHeight="1">
       <c r="A22" t="n">
@@ -21943,6 +21754,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n"/>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 02013-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="46.8" customHeight="1">
       <c r="A23" t="n">
@@ -22045,6 +21861,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n"/>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 02012-1, 03012-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="46.8" customHeight="1">
       <c r="A26" t="n">
@@ -22079,6 +21900,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n"/>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 01212-1, 03012-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="46.8" customHeight="1">
       <c r="A27" t="n">
@@ -22113,6 +21939,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n"/>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 01212-1, 02012-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="46.8" customHeight="1">
       <c r="A28" t="n">
@@ -22759,6 +22590,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n"/>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 12015-1/D — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="46.8" customHeight="1">
       <c r="A47" t="n">
@@ -22963,6 +22799,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n"/>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 12015-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="46.8" customHeight="1">
       <c r="A53" t="n">
@@ -23643,6 +23484,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n"/>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 07021-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="46.8" customHeight="1">
       <c r="A73" t="n">
@@ -23677,6 +23523,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n"/>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 05021-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="46.8" customHeight="1">
       <c r="A74" t="n">
@@ -23711,6 +23562,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n"/>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 05031-6, 06031-6, 07031-6 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="46.8" customHeight="1">
       <c r="A75" t="n">
@@ -23745,6 +23601,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n"/>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 04031-6, 06031-6, 07031-6 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="46.8" customHeight="1">
       <c r="A76" t="n">
@@ -23779,6 +23640,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n"/>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 04031-6, 05031-6, 07031-6 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="46.8" customHeight="1">
       <c r="A77" t="n">
@@ -23813,6 +23679,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n"/>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 04031-6, 05031-6, 06031-6 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="46.8" customHeight="1">
       <c r="A78" t="n">
@@ -23847,6 +23718,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n"/>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 05031-1, 06031-1, 07031-1, 08031-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="46.8" customHeight="1">
       <c r="A79" t="n">
@@ -23881,6 +23757,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n"/>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 04031-1, 06031-1, 07031-1, 08031-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="46.8" customHeight="1">
       <c r="A80" t="n">
@@ -23915,6 +23796,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n"/>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 04031-1, 05031-1, 07031-1, 08031-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="46.8" customHeight="1">
       <c r="A81" t="n">
@@ -23949,6 +23835,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n"/>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 04031-1, 05031-1, 06031-1, 08031-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="46.8" customHeight="1">
       <c r="A82" t="n">
@@ -23983,6 +23874,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n"/>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 04031-1, 05031-1, 06031-1, 07031-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="46.8" customHeight="1">
       <c r="A83" t="n">
@@ -24017,6 +23913,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n"/>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 06092-1, 07092-1, 08092-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="46.8" customHeight="1">
       <c r="A84" t="n">
@@ -24051,6 +23952,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n"/>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 05092-1, 07092-1, 08092-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="46.8" customHeight="1">
       <c r="A85" t="n">
@@ -24085,6 +23991,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n"/>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 05092-1, 06092-1, 08092-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="46.8" customHeight="1">
       <c r="A86" t="n">
@@ -24119,6 +24030,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n"/>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 05092-1, 06092-1, 07092-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="46.8" customHeight="1">
       <c r="A87" t="n">
@@ -24153,6 +24069,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n"/>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 05032-1, 06032-1, 07032-1, 08032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="46.8" customHeight="1">
       <c r="A88" t="n">
@@ -24187,6 +24108,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n"/>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 04032-1, 06032-1, 07032-1, 08032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="46.8" customHeight="1">
       <c r="A89" t="n">
@@ -24221,6 +24147,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n"/>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 04032-1, 05032-1, 07032-1, 08032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="46.8" customHeight="1">
       <c r="A90" t="n">
@@ -24255,6 +24186,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n"/>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 04032-1, 05032-1, 06032-1, 08032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="46.8" customHeight="1">
       <c r="A91" t="n">
@@ -24289,6 +24225,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n"/>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 04032-1, 05032-1, 06032-1, 07032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="46.8" customHeight="1">
       <c r="A92" t="n">
@@ -24357,6 +24298,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n"/>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 26022-3, 27022-3, 28022-3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="46.8" customHeight="1">
       <c r="A94" t="n">
@@ -24391,6 +24337,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n"/>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 25022-3, 27022-3, 28022-3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="46.8" customHeight="1">
       <c r="A95" t="n">
@@ -24425,6 +24376,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n"/>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 25022-3, 26022-3, 28022-3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="46.8" customHeight="1">
       <c r="A96" t="n">
@@ -24459,6 +24415,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n"/>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 25022-3, 26022-3, 27022-3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="46.8" customHeight="1">
       <c r="A97" t="n">
@@ -24493,6 +24454,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n"/>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 05032-6, 06032-6, 07032-6 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="46.8" customHeight="1">
       <c r="A98" t="n">
@@ -24527,6 +24493,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n"/>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 04032-6, 06032-6, 07032-6 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="46.8" customHeight="1">
       <c r="A99" t="n">
@@ -24561,6 +24532,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n"/>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 04032-6, 05032-6, 07032-6 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="46.8" customHeight="1">
       <c r="A100" t="n">
@@ -24595,6 +24571,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n"/>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 04032-6, 05032-6, 06032-6 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="46.8" customHeight="1">
       <c r="A101" t="n">
@@ -24629,6 +24610,11 @@
         </is>
       </c>
       <c r="I101" s="2" t="n"/>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 87032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="46.8" customHeight="1">
       <c r="A102" t="n">
@@ -24663,6 +24649,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="n"/>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 86032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="46.8" customHeight="1">
       <c r="A103" t="n">
@@ -24697,6 +24688,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n"/>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 87031-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="46.8" customHeight="1">
       <c r="A104" t="n">
@@ -24731,6 +24727,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n"/>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 86031-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="46.8" customHeight="1">
       <c r="A105" t="n">
@@ -24799,6 +24800,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n"/>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 01235-1, 01535-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="46.8" customHeight="1">
       <c r="A107" t="n">
@@ -24833,6 +24839,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n"/>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 01035-1, 01535-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="46.8" customHeight="1">
       <c r="A108" t="n">
@@ -24867,6 +24878,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="n"/>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 01035-1, 01235-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="46.8" customHeight="1">
       <c r="A109" t="n">
@@ -24877,6 +24893,11 @@
           <t>02035-1</t>
         </is>
       </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>โค้ดนี้มีสองความหมายในแคตตาล็อก — ดูหน้า Settings</t>
+        </is>
+      </c>
       <c r="D109" t="inlineStr">
         <is>
           <t>tree</t>
@@ -25003,6 +25024,11 @@
         </is>
       </c>
       <c r="I112" s="2" t="n"/>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 07012-2, 08012-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="46.8" customHeight="1">
       <c r="A113" t="n">
@@ -25037,6 +25063,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n"/>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 04072-1, 08012-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="46.8" customHeight="1">
       <c r="A114" t="n">
@@ -25071,6 +25102,11 @@
         </is>
       </c>
       <c r="I114" s="2" t="n"/>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 04072-1, 07012-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="46.8" customHeight="1">
       <c r="A115" t="n">
@@ -25099,6 +25135,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n"/>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 07512-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="46.8" customHeight="1">
       <c r="A116" t="n">
@@ -25133,6 +25174,11 @@
         </is>
       </c>
       <c r="I116" s="2" t="n"/>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 05572-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="46.8" customHeight="1">
       <c r="A117" t="n">
@@ -25201,6 +25247,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="n"/>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 41592-1, 42092-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="46.8" customHeight="1">
       <c r="A119" t="n">
@@ -25235,6 +25286,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n"/>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 41092-1, 42092-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="46.8" customHeight="1">
       <c r="A120" t="n">
@@ -25269,6 +25325,11 @@
         </is>
       </c>
       <c r="I120" s="2" t="n"/>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 41092-1, 41592-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="46.8" customHeight="1">
       <c r="A121" t="n">
@@ -25337,6 +25398,11 @@
         </is>
       </c>
       <c r="I122" s="2" t="n"/>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 26022-2, 27022-2, 28022-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="46.8" customHeight="1">
       <c r="A123" t="n">
@@ -25371,6 +25437,11 @@
         </is>
       </c>
       <c r="I123" s="2" t="n"/>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 25022-2, 27022-2, 28022-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="46.8" customHeight="1">
       <c r="A124" t="n">
@@ -25405,6 +25476,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n"/>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 25022-2, 26022-2, 28022-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="46.8" customHeight="1">
       <c r="A125" t="n">
@@ -25439,6 +25515,11 @@
         </is>
       </c>
       <c r="I125" s="2" t="n"/>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 25022-2, 26022-2, 27022-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="46.8" customHeight="1">
       <c r="A126" t="n">
@@ -25473,6 +25554,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n"/>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 08012-3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="46.8" customHeight="1">
       <c r="A127" t="n">
@@ -25507,6 +25593,11 @@
         </is>
       </c>
       <c r="I127" s="2" t="n"/>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 06012-3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="46.8" customHeight="1">
       <c r="A128" t="n">
@@ -25551,6 +25642,11 @@
           <t>26022-2FK</t>
         </is>
       </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>ไม่ใช่รูปสินค้า (heading)</t>
+        </is>
+      </c>
       <c r="D129" t="inlineStr">
         <is>
           <t>tree</t>
@@ -25585,6 +25681,11 @@
           <t>07012-2FK</t>
         </is>
       </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>ไม่ใช่รูปสินค้า (heading)</t>
+        </is>
+      </c>
       <c r="D130" t="inlineStr">
         <is>
           <t>flower</t>
@@ -25665,6 +25766,11 @@
         </is>
       </c>
       <c r="I132" s="2" t="n"/>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 45032-1, 46032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="46.8" customHeight="1">
       <c r="A133" t="n">
@@ -25699,6 +25805,11 @@
         </is>
       </c>
       <c r="I133" s="2" t="n"/>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 44032-1, 46032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="46.8" customHeight="1">
       <c r="A134" t="n">
@@ -25733,6 +25844,11 @@
         </is>
       </c>
       <c r="I134" s="2" t="n"/>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 44032-1, 45032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="46.8" customHeight="1">
       <c r="A135" t="n">
@@ -25767,6 +25883,11 @@
         </is>
       </c>
       <c r="I135" s="2" t="n"/>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 48032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="46.8" customHeight="1">
       <c r="A136" t="n">
@@ -25801,6 +25922,11 @@
         </is>
       </c>
       <c r="I136" s="2" t="n"/>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 47032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="46.8" customHeight="1">
       <c r="A137" t="n">
@@ -25869,6 +25995,11 @@
         </is>
       </c>
       <c r="I138" s="2" t="n"/>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 37072-1, 34072-1, 36072-1, 38072-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="46.8" customHeight="1">
       <c r="A139" t="n">
@@ -25903,6 +26034,11 @@
         </is>
       </c>
       <c r="I139" s="2" t="n"/>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 35072-1, 34072-1, 36072-1, 38072-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="46.8" customHeight="1">
       <c r="A140" t="n">
@@ -25937,6 +26073,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="n"/>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 38092-5 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="46.8" customHeight="1">
       <c r="A141" t="n">
@@ -25971,6 +26112,11 @@
         </is>
       </c>
       <c r="I141" s="2" t="n"/>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 36092-4 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="46.8" customHeight="1">
       <c r="A142" t="n">
@@ -26005,6 +26151,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n"/>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 36031-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="46.8" customHeight="1">
       <c r="A143" t="n">
@@ -26039,6 +26190,11 @@
         </is>
       </c>
       <c r="I143" s="2" t="n"/>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 35031-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="46.8" customHeight="1">
       <c r="A144" t="n">
@@ -26073,6 +26229,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n"/>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 35072-1, 37072-1, 36072-1, 38072-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="46.8" customHeight="1">
       <c r="A145" t="n">
@@ -26107,6 +26268,11 @@
         </is>
       </c>
       <c r="I145" s="2" t="n"/>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 35072-1, 37072-1, 34072-1, 38072-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="46.8" customHeight="1">
       <c r="A146" t="n">
@@ -26141,6 +26307,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="n"/>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 35072-1, 37072-1, 34072-1, 36072-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="46.8" customHeight="1">
       <c r="A147" t="n">
@@ -26855,6 +27026,11 @@
         </is>
       </c>
       <c r="I167" s="2" t="n"/>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 56614-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="46.8" customHeight="1">
       <c r="A168" t="n">
@@ -26991,6 +27167,11 @@
         </is>
       </c>
       <c r="I171" s="2" t="n"/>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 56614-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="46.8" customHeight="1">
       <c r="A172" t="n">
@@ -27059,6 +27240,11 @@
         </is>
       </c>
       <c r="I173" s="2" t="n"/>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 56718-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="46.8" customHeight="1">
       <c r="A174" t="n">
@@ -27195,6 +27381,11 @@
         </is>
       </c>
       <c r="I177" s="2" t="n"/>
+      <c r="J177" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 53618-5 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="46.8" customHeight="1">
       <c r="A178" t="n">
@@ -27297,6 +27488,11 @@
         </is>
       </c>
       <c r="I180" s="2" t="n"/>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 55820-1, 55924-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="46.8" customHeight="1">
       <c r="A181" t="n">
@@ -27331,6 +27527,11 @@
         </is>
       </c>
       <c r="I181" s="2" t="n"/>
+      <c r="J181" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 56918-1, 55924-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="46.8" customHeight="1">
       <c r="A182" t="n">
@@ -27365,6 +27566,11 @@
         </is>
       </c>
       <c r="I182" s="2" t="n"/>
+      <c r="J182" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 56918-1, 55820-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="46.8" customHeight="1">
       <c r="A183" t="n">
@@ -27665,6 +27871,11 @@
         </is>
       </c>
       <c r="I191" s="2" t="n"/>
+      <c r="J191" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 71016-1/DR/66 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="46.8" customHeight="1">
       <c r="A192" t="n">
@@ -27721,6 +27932,11 @@
         </is>
       </c>
       <c r="I193" s="2" t="n"/>
+      <c r="J193" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 71016-1/DG/66 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="46.8" customHeight="1">
       <c r="A194" t="n">
@@ -27805,6 +28021,11 @@
         </is>
       </c>
       <c r="I196" s="2" t="n"/>
+      <c r="J196" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 74026-1/D2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="46.8" customHeight="1">
       <c r="A197" t="n">
@@ -27861,6 +28082,11 @@
         </is>
       </c>
       <c r="I198" s="2" t="n"/>
+      <c r="J198" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 74026-1/D1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="46.8" customHeight="1">
       <c r="A199" t="n">
@@ -27945,6 +28171,11 @@
         </is>
       </c>
       <c r="I201" s="2" t="n"/>
+      <c r="J201" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 60801-1, 60959-1, 61001-1, 60851-1, 61002-1, 60852-1, 60850-6, 61004-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="46.8" customHeight="1">
       <c r="A202" t="n">
@@ -27973,6 +28204,11 @@
         </is>
       </c>
       <c r="I202" s="2" t="n"/>
+      <c r="J202" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 60850-2, 60959-1, 61001-1, 60851-1, 61002-1, 60852-1, 60850-6, 61004-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="46.8" customHeight="1">
       <c r="A203" t="n">
@@ -28001,6 +28237,11 @@
         </is>
       </c>
       <c r="I203" s="2" t="n"/>
+      <c r="J203" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 60850-2, 60801-1, 61001-1, 60851-1, 61002-1, 60852-1, 60850-6, 61004-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="46.8" customHeight="1">
       <c r="A204" t="n">
@@ -28029,6 +28270,11 @@
         </is>
       </c>
       <c r="I204" s="2" t="n"/>
+      <c r="J204" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 60850-2, 60801-1, 60959-1, 60851-1, 61002-1, 60852-1, 60850-6, 61004-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="46.8" customHeight="1">
       <c r="A205" t="n">
@@ -28057,6 +28303,11 @@
         </is>
       </c>
       <c r="I205" s="2" t="n"/>
+      <c r="J205" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 60850-2, 60801-1, 60959-1, 61001-1, 61002-1, 60852-1, 60850-6, 61004-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="46.8" customHeight="1">
       <c r="A206" t="n">
@@ -28085,6 +28336,11 @@
         </is>
       </c>
       <c r="I206" s="2" t="n"/>
+      <c r="J206" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 60850-2, 60801-1, 60959-1, 61001-1, 60851-1, 60852-1, 60850-6, 61004-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="46.8" customHeight="1">
       <c r="A207" t="n">
@@ -28113,6 +28369,11 @@
         </is>
       </c>
       <c r="I207" s="2" t="n"/>
+      <c r="J207" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 60850-2, 60801-1, 60959-1, 61001-1, 60851-1, 61002-1, 60850-6, 61004-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="46.8" customHeight="1">
       <c r="A208" t="n">
@@ -28141,6 +28402,11 @@
         </is>
       </c>
       <c r="I208" s="2" t="n"/>
+      <c r="J208" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 60850-2, 60801-1, 60959-1, 61001-1, 60851-1, 61002-1, 60852-1, 61004-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="46.8" customHeight="1">
       <c r="A209" t="n">
@@ -28169,6 +28435,11 @@
         </is>
       </c>
       <c r="I209" s="2" t="n"/>
+      <c r="J209" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 61056-1, 61256-1, 61055-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="46.8" customHeight="1">
       <c r="A210" t="n">
@@ -28197,6 +28468,11 @@
         </is>
       </c>
       <c r="I210" s="2" t="n"/>
+      <c r="J210" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 61202-1, 61205-1, 61255-3, 61059-1, 61255-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="46.8" customHeight="1">
       <c r="A211" t="n">
@@ -28225,6 +28501,11 @@
         </is>
       </c>
       <c r="I211" s="2" t="n"/>
+      <c r="J211" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 61052-1, 61205-1, 61255-3, 61059-1, 61255-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="46.8" customHeight="1">
       <c r="A212" t="n">
@@ -28253,6 +28534,11 @@
         </is>
       </c>
       <c r="I212" s="2" t="n"/>
+      <c r="J212" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 61052-1, 61202-1, 61255-3, 61059-1, 61255-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="46.8" customHeight="1">
       <c r="A213" t="n">
@@ -28281,6 +28567,11 @@
         </is>
       </c>
       <c r="I213" s="2" t="n"/>
+      <c r="J213" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 61058-1, 61256-1, 61055-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="46.8" customHeight="1">
       <c r="A214" t="n">
@@ -28309,6 +28600,11 @@
         </is>
       </c>
       <c r="I214" s="2" t="n"/>
+      <c r="J214" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 61052-1, 61202-1, 61205-1, 61059-1, 61255-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="46.8" customHeight="1">
       <c r="A215" t="n">
@@ -28337,6 +28633,11 @@
         </is>
       </c>
       <c r="I215" s="2" t="n"/>
+      <c r="J215" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 61052-1, 61202-1, 61205-1, 61255-3, 61255-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="46.8" customHeight="1">
       <c r="A216" t="n">
@@ -28365,6 +28666,11 @@
         </is>
       </c>
       <c r="I216" s="2" t="n"/>
+      <c r="J216" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 60850-2, 60801-1, 60959-1, 61001-1, 60851-1, 61002-1, 60852-1, 60850-6 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="46.8" customHeight="1">
       <c r="A217" t="n">
@@ -28393,6 +28699,11 @@
         </is>
       </c>
       <c r="I217" s="2" t="n"/>
+      <c r="J217" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 61058-1, 61056-1, 61055-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="46.8" customHeight="1">
       <c r="A218" t="n">
@@ -28421,6 +28732,11 @@
         </is>
       </c>
       <c r="I218" s="2" t="n"/>
+      <c r="J218" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 61058-1, 61056-1, 61256-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="46.8" customHeight="1">
       <c r="A219" t="n">
@@ -28449,6 +28765,11 @@
         </is>
       </c>
       <c r="I219" s="2" t="n"/>
+      <c r="J219" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 61052-1, 61202-1, 61205-1, 61255-3, 61059-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="46.8" customHeight="1">
       <c r="A220" t="n">
@@ -28527,6 +28848,11 @@
           <t>70912-4</t>
         </is>
       </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>ไม่ใช่รูปสินค้า (page_number)</t>
+        </is>
+      </c>
       <c r="D222" t="inlineStr">
         <is>
           <t>wreath</t>
@@ -28687,6 +29013,11 @@
         </is>
       </c>
       <c r="I226" s="2" t="n"/>
+      <c r="J226" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 70912-3/D1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="46.8" customHeight="1">
       <c r="A227" t="n">
@@ -28721,6 +29052,11 @@
         </is>
       </c>
       <c r="I227" s="2" t="n"/>
+      <c r="J227" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 70912-4/D — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="46.8" customHeight="1">
       <c r="A228" t="n">
@@ -28919,6 +29255,11 @@
         </is>
       </c>
       <c r="I233" s="2" t="n"/>
+      <c r="J233" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 70912-4/D3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="46.8" customHeight="1">
       <c r="A234" t="n">
@@ -28953,6 +29294,11 @@
         </is>
       </c>
       <c r="I234" s="2" t="n"/>
+      <c r="J234" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 70612-2/D2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="46.8" customHeight="1">
       <c r="A235" t="n">
@@ -29021,6 +29367,11 @@
         </is>
       </c>
       <c r="I236" s="2" t="n"/>
+      <c r="J236" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 70023-4 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="46.8" customHeight="1">
       <c r="A237" t="n">
@@ -29055,6 +29406,11 @@
         </is>
       </c>
       <c r="I237" s="2" t="n"/>
+      <c r="J237" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 70412-3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="46.8" customHeight="1">
       <c r="A238" t="n">
@@ -29955,6 +30311,11 @@
         </is>
       </c>
       <c r="I264" s="2" t="n"/>
+      <c r="J264" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 039-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="46.8" customHeight="1">
       <c r="A265" t="n">
@@ -29989,6 +30350,11 @@
         </is>
       </c>
       <c r="I265" s="2" t="n"/>
+      <c r="J265" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 017-08 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="46.8" customHeight="1">
       <c r="A266" t="n">
@@ -30617,6 +30983,11 @@
         </is>
       </c>
       <c r="I284" s="2" t="n"/>
+      <c r="J284" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 053-06 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="46.8" customHeight="1">
       <c r="A285" t="n">
@@ -30651,6 +31022,11 @@
         </is>
       </c>
       <c r="I285" s="2" t="n"/>
+      <c r="J285" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 059-07 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="46.8" customHeight="1">
       <c r="A286" t="n">
@@ -31367,6 +31743,11 @@
         </is>
       </c>
       <c r="I308" s="2" t="n"/>
+      <c r="J308" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 107-03, 107-04 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="309" ht="46.8" customHeight="1">
       <c r="A309" t="n">
@@ -31451,6 +31832,11 @@
         </is>
       </c>
       <c r="I311" s="2" t="n"/>
+      <c r="J311" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 107-02, 107-04 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="312" ht="46.8" customHeight="1">
       <c r="A312" t="n">
@@ -31479,6 +31865,11 @@
         </is>
       </c>
       <c r="I312" s="2" t="n"/>
+      <c r="J312" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 107-02, 107-03 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="313" ht="46.8" customHeight="1">
       <c r="A313" t="n">
@@ -31959,6 +32350,11 @@
         </is>
       </c>
       <c r="I327" s="2" t="n"/>
+      <c r="J327" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 048-02, 073-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="328" ht="46.8" customHeight="1">
       <c r="A328" t="n">
@@ -31993,6 +32389,11 @@
         </is>
       </c>
       <c r="I328" s="2" t="n"/>
+      <c r="J328" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 047-02, 073-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="329" ht="46.8" customHeight="1">
       <c r="A329" t="n">
@@ -32027,6 +32428,11 @@
         </is>
       </c>
       <c r="I329" s="2" t="n"/>
+      <c r="J329" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 047-02, 048-02 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="330" ht="46.8" customHeight="1">
       <c r="A330" t="n">
@@ -32163,6 +32569,11 @@
         </is>
       </c>
       <c r="I333" s="2" t="n"/>
+      <c r="J333" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 90251-1, 90252-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="334" ht="46.8" customHeight="1">
       <c r="A334" t="n">
@@ -32197,6 +32608,11 @@
         </is>
       </c>
       <c r="I334" s="2" t="n"/>
+      <c r="J334" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 90253-3, 90252-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="335" ht="46.8" customHeight="1">
       <c r="A335" t="n">
@@ -32231,6 +32647,11 @@
         </is>
       </c>
       <c r="I335" s="2" t="n"/>
+      <c r="J335" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 90253-3, 90251-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="336" ht="46.8" customHeight="1">
       <c r="A336" t="n">
@@ -32265,6 +32686,11 @@
         </is>
       </c>
       <c r="I336" s="2" t="n"/>
+      <c r="J336" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 90232-8 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="337" ht="46.8" customHeight="1">
       <c r="A337" t="n">
@@ -32299,6 +32725,11 @@
         </is>
       </c>
       <c r="I337" s="2" t="n"/>
+      <c r="J337" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 90249-3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="338" ht="46.8" customHeight="1">
       <c r="A338" t="n">
@@ -33091,6 +33522,11 @@
         </is>
       </c>
       <c r="I361" s="2" t="n"/>
+      <c r="J361" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 90564-4 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="362" ht="46.8" customHeight="1">
       <c r="A362" t="n">
@@ -33119,6 +33555,11 @@
         </is>
       </c>
       <c r="I362" s="2" t="n"/>
+      <c r="J362" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 90577-3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="363" ht="46.8" customHeight="1">
       <c r="A363" t="n">
@@ -34335,6 +34776,11 @@
         </is>
       </c>
       <c r="I405" s="2" t="n"/>
+      <c r="J405" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 6121-02 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="406" ht="46.8" customHeight="1">
       <c r="A406" t="n">
@@ -34369,6 +34815,11 @@
         </is>
       </c>
       <c r="I406" s="2" t="n"/>
+      <c r="J406" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 6121-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="407" ht="46.8" customHeight="1">
       <c r="A407" t="n">
@@ -34453,6 +34904,11 @@
         </is>
       </c>
       <c r="I409" s="2" t="n"/>
+      <c r="J409" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 90767-3, 90773-1, 90774-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="410" ht="46.8" customHeight="1">
       <c r="A410" t="n">
@@ -34481,6 +34937,11 @@
         </is>
       </c>
       <c r="I410" s="2" t="n"/>
+      <c r="J410" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 90772-1, 90773-1, 90774-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="411" ht="46.8" customHeight="1">
       <c r="A411" t="n">
@@ -34515,6 +34976,11 @@
         </is>
       </c>
       <c r="I411" s="2" t="n"/>
+      <c r="J411" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 6704-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="412" ht="46.8" customHeight="1">
       <c r="A412" t="n">
@@ -34549,6 +35015,11 @@
         </is>
       </c>
       <c r="I412" s="2" t="n"/>
+      <c r="J412" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 6703-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="413" ht="46.8" customHeight="1">
       <c r="A413" t="n">
@@ -34633,6 +35104,11 @@
         </is>
       </c>
       <c r="I415" s="2" t="n"/>
+      <c r="J415" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 90772-1, 90767-3, 90774-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="416" ht="46.8" customHeight="1">
       <c r="A416" t="n">
@@ -34661,6 +35137,11 @@
         </is>
       </c>
       <c r="I416" s="2" t="n"/>
+      <c r="J416" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 90772-1, 90767-3, 90773-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="417" ht="46.8" customHeight="1">
       <c r="A417" t="n">
@@ -34723,6 +35204,11 @@
         </is>
       </c>
       <c r="I418" s="2" t="n"/>
+      <c r="J418" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 6753-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="419" ht="46.8" customHeight="1">
       <c r="A419" t="n">
@@ -34757,6 +35243,11 @@
         </is>
       </c>
       <c r="I419" s="2" t="n"/>
+      <c r="J419" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 6754-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="420" ht="46.8" customHeight="1">
       <c r="A420" t="n">
@@ -34791,6 +35282,11 @@
         </is>
       </c>
       <c r="I420" s="2" t="n"/>
+      <c r="J420" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 6120-02 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="421" ht="46.8" customHeight="1">
       <c r="A421" t="n">
@@ -34825,6 +35321,11 @@
         </is>
       </c>
       <c r="I421" s="2" t="n"/>
+      <c r="J421" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 6120-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="422" ht="46.8" customHeight="1">
       <c r="A422" t="n">
@@ -35225,6 +35726,11 @@
         </is>
       </c>
       <c r="I434" s="2" t="n"/>
+      <c r="J434" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 6384-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="435" ht="46.8" customHeight="1">
       <c r="A435" t="n">
@@ -35259,6 +35765,11 @@
         </is>
       </c>
       <c r="I435" s="2" t="n"/>
+      <c r="J435" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 6730-02 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="436" ht="46.8" customHeight="1">
       <c r="A436" t="n">
@@ -35325,6 +35836,11 @@
           <t>90634-8</t>
         </is>
       </c>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>โค้ดนี้มีสองความหมายในแคตตาล็อก — ดูหน้า Settings</t>
+        </is>
+      </c>
       <c r="D438" t="inlineStr">
         <is>
           <t>ornament</t>
@@ -35349,6 +35865,11 @@
         </is>
       </c>
       <c r="I438" s="2" t="n"/>
+      <c r="J438" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 90663-18 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="439" ht="46.8" customHeight="1">
       <c r="A439" t="n">
@@ -35359,6 +35880,11 @@
           <t>90663-18</t>
         </is>
       </c>
+      <c r="C439" s="2" t="inlineStr">
+        <is>
+          <t>โค้ดนี้มีสองความหมายในแคตตาล็อก — ดูหน้า Settings</t>
+        </is>
+      </c>
       <c r="D439" t="inlineStr">
         <is>
           <t>ornament</t>
@@ -35383,6 +35909,11 @@
         </is>
       </c>
       <c r="I439" s="2" t="n"/>
+      <c r="J439" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 90634-8 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="440" ht="46.8" customHeight="1">
       <c r="A440" t="n">
@@ -35835,6 +36366,11 @@
         </is>
       </c>
       <c r="I453" s="2" t="n"/>
+      <c r="J453" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 90707-2, 90755-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="454" ht="46.8" customHeight="1">
       <c r="A454" t="n">
@@ -35869,6 +36405,11 @@
         </is>
       </c>
       <c r="I454" s="2" t="n"/>
+      <c r="J454" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 90754-3, 90755-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="455" ht="46.8" customHeight="1">
       <c r="A455" t="n">
@@ -35903,6 +36444,11 @@
         </is>
       </c>
       <c r="I455" s="2" t="n"/>
+      <c r="J455" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 90754-3, 90707-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="456" ht="46.8" customHeight="1">
       <c r="A456" t="n">
@@ -36415,6 +36961,11 @@
         </is>
       </c>
       <c r="I472" s="2" t="n"/>
+      <c r="J472" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 5713-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="473" ht="46.8" customHeight="1">
       <c r="A473" t="n">
@@ -36443,6 +36994,11 @@
         </is>
       </c>
       <c r="I473" s="2" t="n"/>
+      <c r="J473" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 5702-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="474" ht="46.8" customHeight="1">
       <c r="A474" t="n">
@@ -36583,6 +37139,11 @@
         </is>
       </c>
       <c r="I478" s="2" t="n"/>
+      <c r="J478" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 72033-1, 73033-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="479" ht="46.8" customHeight="1">
       <c r="A479" t="n">
@@ -36611,6 +37172,11 @@
         </is>
       </c>
       <c r="I479" s="2" t="n"/>
+      <c r="J479" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 71533-1, 73033-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="480" ht="46.8" customHeight="1">
       <c r="A480" t="n">
@@ -36639,6 +37205,11 @@
         </is>
       </c>
       <c r="I480" s="2" t="n"/>
+      <c r="J480" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 71533-1, 72033-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="481" ht="46.8" customHeight="1">
       <c r="A481" t="n">
@@ -37115,6 +37686,11 @@
         </is>
       </c>
       <c r="I497" s="2" t="n"/>
+      <c r="J497" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 5871-02 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="498" ht="46.8" customHeight="1">
       <c r="A498" t="n">
@@ -37143,6 +37719,11 @@
         </is>
       </c>
       <c r="I498" s="2" t="n"/>
+      <c r="J498" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 5871-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="499" ht="46.8" customHeight="1">
       <c r="A499" t="n">
@@ -37339,6 +37920,11 @@
         </is>
       </c>
       <c r="I505" s="2" t="n"/>
+      <c r="J505" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 5890-03 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="506" ht="46.8" customHeight="1">
       <c r="A506" t="n">
@@ -37367,6 +37953,11 @@
         </is>
       </c>
       <c r="I506" s="2" t="n"/>
+      <c r="J506" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 5871-03 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="507" ht="46.8" customHeight="1">
       <c r="A507" t="n">
@@ -39415,6 +40006,11 @@
           <t>90680-6</t>
         </is>
       </c>
+      <c r="C574" s="2" t="inlineStr">
+        <is>
+          <t>โค้ดนี้มีสองความหมายในแคตตาล็อก — ดูหน้า Settings</t>
+        </is>
+      </c>
       <c r="D574" t="inlineStr">
         <is>
           <t>flower</t>
@@ -40145,6 +40741,11 @@
         </is>
       </c>
       <c r="I596" s="2" t="n"/>
+      <c r="J596" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 90586-4 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="597" ht="46.8" customHeight="1">
       <c r="A597" t="n">
@@ -40173,6 +40774,11 @@
         </is>
       </c>
       <c r="I597" s="2" t="n"/>
+      <c r="J597" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 90586-3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="598" ht="46.8" customHeight="1">
       <c r="A598" t="n">
@@ -40759,6 +41365,11 @@
           <t>6125-01</t>
         </is>
       </c>
+      <c r="C616" s="2" t="inlineStr">
+        <is>
+          <t>ไม่ใช่รูปสินค้า (logo)</t>
+        </is>
+      </c>
       <c r="D616" t="inlineStr">
         <is>
           <t>topper</t>
@@ -40805,6 +41416,11 @@
         </is>
       </c>
       <c r="I617" s="2" t="n"/>
+      <c r="J617" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 6124-02 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="618" ht="46.8" customHeight="1">
       <c r="A618" t="n">
@@ -40833,6 +41449,11 @@
         </is>
       </c>
       <c r="I618" s="2" t="n"/>
+      <c r="J618" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 6117-07 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="619" ht="46.8" customHeight="1">
       <c r="A619" t="n">
@@ -40929,6 +41550,11 @@
         </is>
       </c>
       <c r="I621" s="2" t="n"/>
+      <c r="J621" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 6114-05, 6191-03 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="622" ht="46.8" customHeight="1">
       <c r="A622" t="n">
@@ -40963,6 +41589,11 @@
         </is>
       </c>
       <c r="I622" s="2" t="n"/>
+      <c r="J622" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 6111-02, 6191-03 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="623" ht="46.8" customHeight="1">
       <c r="A623" t="n">
@@ -40997,6 +41628,11 @@
         </is>
       </c>
       <c r="I623" s="2" t="n"/>
+      <c r="J623" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 6111-02, 6114-05 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="624" ht="46.8" customHeight="1">
       <c r="A624" t="n">
@@ -41031,6 +41667,11 @@
         </is>
       </c>
       <c r="I624" s="2" t="n"/>
+      <c r="J624" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 90698-5 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="625" ht="46.8" customHeight="1">
       <c r="A625" t="n">
@@ -41065,6 +41706,11 @@
         </is>
       </c>
       <c r="I625" s="2" t="n"/>
+      <c r="J625" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 90651-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="626" ht="46.8" customHeight="1">
       <c r="A626" t="n">
@@ -41235,6 +41881,11 @@
         </is>
       </c>
       <c r="I630" s="2" t="n"/>
+      <c r="J630" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 79015-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="631" ht="46.8" customHeight="1">
       <c r="A631" t="n">
@@ -41269,6 +41920,11 @@
         </is>
       </c>
       <c r="I631" s="2" t="n"/>
+      <c r="J631" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 76015-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="632" ht="46.8" customHeight="1">
       <c r="A632" t="n">
@@ -41337,6 +41993,11 @@
         </is>
       </c>
       <c r="I633" s="2" t="n"/>
+      <c r="J633" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 76015-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="634" ht="46.8" customHeight="1">
       <c r="A634" t="n">
@@ -41371,6 +42032,11 @@
         </is>
       </c>
       <c r="I634" s="2" t="n"/>
+      <c r="J634" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 79015-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="635" ht="46.8" customHeight="1">
       <c r="A635" t="n">
@@ -41461,6 +42127,11 @@
         </is>
       </c>
       <c r="I637" s="2" t="n"/>
+      <c r="J637" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 76015-3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="638" ht="46.8" customHeight="1">
       <c r="A638" t="n">
@@ -41489,6 +42160,11 @@
         </is>
       </c>
       <c r="I638" s="2" t="n"/>
+      <c r="J638" s="3" t="inlineStr">
+        <is>
+          <t>รูปนี้ใช้ร่วมกับ 71015-5 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
+        </is>
+      </c>
     </row>
     <row r="639" ht="46.8" customHeight="1">
       <c r="A639" t="n">

--- a/catalog/product_worksheet.xlsx
+++ b/catalog/product_worksheet.xlsx
@@ -21337,7 +21337,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>ชมพู, น้ำเงิน, เงิน, ทอง, แดง, เขียว</t>
         </is>
       </c>
       <c r="I10" s="2" t="n"/>
@@ -21405,7 +21405,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>purple</t>
+          <t>ม่วง, ชมพู, เขียวสด</t>
         </is>
       </c>
       <c r="I12" s="2" t="n"/>
@@ -21575,7 +21575,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดง, สีเงิน, ทอง</t>
         </is>
       </c>
       <c r="I17" s="2" t="n"/>
@@ -22144,7 +22144,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ทอง, เงิน, เขียว, ทอง</t>
         </is>
       </c>
       <c r="I33" s="2" t="n"/>
@@ -22416,7 +22416,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>เขียว, เขียว</t>
         </is>
       </c>
       <c r="I41" s="2" t="n"/>
@@ -22450,7 +22450,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>ชมพู, ชมพู, ชมพู</t>
         </is>
       </c>
       <c r="I42" s="2" t="n"/>
@@ -25957,7 +25957,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>เขียวขาว, ขาว</t>
         </is>
       </c>
       <c r="I137" s="2" t="n"/>
@@ -26920,7 +26920,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ทอง, เขียวทอง</t>
         </is>
       </c>
       <c r="I164" s="2" t="n"/>
@@ -28907,7 +28907,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>เขียวเข้ม, เขียว, เขียว</t>
         </is>
       </c>
       <c r="I223" s="2" t="n"/>
@@ -29463,7 +29463,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>เขียวเข้ม, เขียวเข้ม</t>
         </is>
       </c>
       <c r="I239" s="2" t="n"/>
@@ -29491,7 +29491,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>เขียวเข้ม, เขียวเข้ม</t>
         </is>
       </c>
       <c r="I240" s="2" t="n"/>
@@ -29559,7 +29559,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>เขียว, เหลือง, น้ำเงิน</t>
         </is>
       </c>
       <c r="I242" s="2" t="n"/>
@@ -29593,7 +29593,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>yellow</t>
+          <t>สีแดง, น้ำเงิน</t>
         </is>
       </c>
       <c r="I243" s="2" t="n"/>
@@ -29661,7 +29661,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ทอง, สีเขียวทอง</t>
         </is>
       </c>
       <c r="I245" s="2" t="n"/>
@@ -29729,7 +29729,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>yellow</t>
+          <t>เหลือง, น้ำเงิน</t>
         </is>
       </c>
       <c r="I247" s="2" t="n"/>
@@ -29763,7 +29763,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>ส้ม, เขียว</t>
         </is>
       </c>
       <c r="I248" s="2" t="n"/>
@@ -29797,7 +29797,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดง, แดง, ทอง</t>
         </is>
       </c>
       <c r="I249" s="2" t="n"/>
@@ -29831,7 +29831,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดง, ส้ม</t>
         </is>
       </c>
       <c r="I250" s="2" t="n"/>
@@ -29865,7 +29865,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดง, เขียว, เหลือง</t>
         </is>
       </c>
       <c r="I251" s="2" t="n"/>
@@ -29899,7 +29899,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดง, สีเขียว</t>
         </is>
       </c>
       <c r="I252" s="2" t="n"/>
@@ -30001,7 +30001,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดง, ทอง, หลากสี</t>
         </is>
       </c>
       <c r="I255" s="2" t="n"/>
@@ -30137,7 +30137,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>yellow</t>
+          <t>เหลือง, แดง</t>
         </is>
       </c>
       <c r="I259" s="2" t="n"/>
@@ -30385,7 +30385,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>ขาว, ขาว</t>
         </is>
       </c>
       <c r="I266" s="2" t="n"/>
@@ -30589,7 +30589,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t>ทองแดง, ทองแดง, ทองแดง</t>
         </is>
       </c>
       <c r="I272" s="2" t="n"/>
@@ -30651,7 +30651,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>ชมพูทอง, ชมพูโรสโกลด์</t>
         </is>
       </c>
       <c r="I274" s="2" t="n"/>
@@ -30741,7 +30741,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ทอง, ทองแดง</t>
         </is>
       </c>
       <c r="I277" s="2" t="n"/>
@@ -30877,7 +30877,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดง, สีแดง</t>
         </is>
       </c>
       <c r="I281" s="2" t="n"/>
@@ -30945,7 +30945,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดง, แดง</t>
         </is>
       </c>
       <c r="I283" s="2" t="n"/>
@@ -31057,7 +31057,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>สีน้ำเงิน, สีเขียว</t>
         </is>
       </c>
       <c r="I286" s="2" t="n"/>
@@ -31345,7 +31345,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>ชมพู, สีน้ำเงิน</t>
         </is>
       </c>
       <c r="I295" s="2" t="n"/>
@@ -31503,7 +31503,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ทอง, แดง</t>
         </is>
       </c>
       <c r="I300" s="2" t="n"/>
@@ -31655,7 +31655,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดง, เขียว</t>
         </is>
       </c>
       <c r="I305" s="2" t="n"/>
@@ -31711,7 +31711,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>ขาวแดง, แดงขาว, แดงขาว, แดง</t>
         </is>
       </c>
       <c r="I307" s="2" t="n"/>
@@ -31900,7 +31900,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ทอง, ทอง, ทอง</t>
         </is>
       </c>
       <c r="I313" s="2" t="n"/>
@@ -31934,7 +31934,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดง, แดง</t>
         </is>
       </c>
       <c r="I314" s="2" t="n"/>
@@ -31996,7 +31996,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดง, แดง</t>
         </is>
       </c>
       <c r="I316" s="2" t="n"/>
@@ -32030,7 +32030,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ทอง, ทอง, ทอง</t>
         </is>
       </c>
       <c r="I317" s="2" t="n"/>
@@ -32188,7 +32188,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t>เงิน, ทองอ่อน</t>
         </is>
       </c>
       <c r="I322" s="2" t="n"/>
@@ -32278,7 +32278,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>เขียว, แดง, ทอง</t>
         </is>
       </c>
       <c r="I325" s="2" t="n"/>
@@ -32828,7 +32828,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t>เงิน, แดง</t>
         </is>
       </c>
       <c r="I340" s="2" t="n"/>
@@ -32896,7 +32896,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t>เงิน, ทอง</t>
         </is>
       </c>
       <c r="I342" s="2" t="n"/>
@@ -33462,7 +33462,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>เงิน, ขาว</t>
         </is>
       </c>
       <c r="I359" s="2" t="n"/>
@@ -33590,7 +33590,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>เขียวอมเหลือง, แดงเขียว</t>
         </is>
       </c>
       <c r="I363" s="2" t="n"/>
@@ -33618,7 +33618,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t>สีเงิน, เงิน</t>
         </is>
       </c>
       <c r="I364" s="2" t="n"/>
@@ -33758,7 +33758,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>เหลืองอ่อน, ทอง</t>
         </is>
       </c>
       <c r="I369" s="2" t="n"/>
@@ -33814,7 +33814,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ทอง, สีทอง</t>
         </is>
       </c>
       <c r="I371" s="2" t="n"/>
@@ -33842,7 +33842,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ทอง, ขาว</t>
         </is>
       </c>
       <c r="I372" s="2" t="n"/>
@@ -33926,7 +33926,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ทอง, ทอง</t>
         </is>
       </c>
       <c r="I375" s="2" t="n"/>
@@ -34038,7 +34038,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ทอง, ทอง</t>
         </is>
       </c>
       <c r="I379" s="2" t="n"/>
@@ -34094,7 +34094,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดง, แดง</t>
         </is>
       </c>
       <c r="I381" s="2" t="n"/>
@@ -34122,7 +34122,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>เขียว, เขียว, เขียว</t>
         </is>
       </c>
       <c r="I382" s="2" t="n"/>
@@ -34150,7 +34150,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>ขาว, ขาว</t>
         </is>
       </c>
       <c r="I383" s="2" t="n"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดง, ขาวแดง</t>
         </is>
       </c>
       <c r="I387" s="2" t="n"/>
@@ -34290,7 +34290,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>ขาว, แดง, แดง</t>
         </is>
       </c>
       <c r="I388" s="2" t="n"/>
@@ -34346,7 +34346,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดง, แดง</t>
         </is>
       </c>
       <c r="I390" s="2" t="n"/>
@@ -34374,7 +34374,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>สีทอง, สีทอง</t>
         </is>
       </c>
       <c r="I391" s="2" t="n"/>
@@ -34458,7 +34458,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดงขาว, แดง</t>
         </is>
       </c>
       <c r="I394" s="2" t="n"/>
@@ -34542,7 +34542,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>ขาว, เหลือง</t>
         </is>
       </c>
       <c r="I397" s="2" t="n"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>หลากสี, สีรุ้ง</t>
         </is>
       </c>
       <c r="I399" s="2" t="n"/>
@@ -34844,7 +34844,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>น้ำตาลอ่อน, น้ำตาลทอง</t>
         </is>
       </c>
       <c r="I407" s="2" t="n"/>
@@ -35166,7 +35166,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>ทองอมชมพู, สีทอง</t>
         </is>
       </c>
       <c r="I417" s="2" t="n"/>
@@ -35356,7 +35356,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ทอง, ทอง</t>
         </is>
       </c>
       <c r="I422" s="2" t="n"/>
@@ -35412,7 +35412,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ทอง, ทอง</t>
         </is>
       </c>
       <c r="I424" s="2" t="n"/>
@@ -35552,7 +35552,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>ขาว, ขาว</t>
         </is>
       </c>
       <c r="I429" s="2" t="n"/>
@@ -35794,7 +35794,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดงขาว, แดงขาว</t>
         </is>
       </c>
       <c r="I436" s="2" t="n"/>
@@ -35972,7 +35972,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>แดงทอง, ทองแดง</t>
         </is>
       </c>
       <c r="I441" s="2" t="n"/>
@@ -36040,7 +36040,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ทอง, ทอง</t>
         </is>
       </c>
       <c r="I443" s="2" t="n"/>
@@ -36136,7 +36136,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดง, แดงขาว</t>
         </is>
       </c>
       <c r="I446" s="2" t="n"/>
@@ -36479,7 +36479,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดง, ทอง, เงิน</t>
         </is>
       </c>
       <c r="I456" s="2" t="n"/>
@@ -36513,7 +36513,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดง, ทอง</t>
         </is>
       </c>
       <c r="I457" s="2" t="n"/>
@@ -36699,7 +36699,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดง, ทอง</t>
         </is>
       </c>
       <c r="I463" s="2" t="n"/>
@@ -36727,7 +36727,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>multi</t>
+          <t>เขียว, เขียว, ม่วง</t>
         </is>
       </c>
       <c r="I464" s="2" t="n"/>
@@ -36873,7 +36873,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>เขียว, แดง</t>
         </is>
       </c>
       <c r="I469" s="2" t="n"/>
@@ -37107,7 +37107,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>เขียว, เขียวแดง</t>
         </is>
       </c>
       <c r="I477" s="2" t="n"/>
@@ -37262,7 +37262,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>เหลือง, เหลือง</t>
         </is>
       </c>
       <c r="I482" s="2" t="n"/>
@@ -37346,7 +37346,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ทอง, ทอง</t>
         </is>
       </c>
       <c r="I485" s="2" t="n"/>
@@ -37374,7 +37374,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>สีทอง, สีทอง</t>
         </is>
       </c>
       <c r="I486" s="2" t="n"/>
@@ -37430,7 +37430,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดง, เขียว, สีทอง</t>
         </is>
       </c>
       <c r="I488" s="2" t="n"/>
@@ -37570,7 +37570,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ครีมทอง, ทอง</t>
         </is>
       </c>
       <c r="I493" s="2" t="n"/>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t>สีเทา, เงิน</t>
         </is>
       </c>
       <c r="I494" s="2" t="n"/>
@@ -37748,7 +37748,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>สีทอง, ทอง</t>
         </is>
       </c>
       <c r="I499" s="2" t="n"/>
@@ -37888,7 +37888,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t>เงิน, ทอง</t>
         </is>
       </c>
       <c r="I504" s="2" t="n"/>
@@ -38150,7 +38150,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>สีแดง, แดง</t>
         </is>
       </c>
       <c r="I513" s="2" t="n"/>
@@ -38262,7 +38262,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>เขียว, เขียว</t>
         </is>
       </c>
       <c r="I517" s="2" t="n"/>
@@ -38374,7 +38374,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>เหลือง, เหลือง</t>
         </is>
       </c>
       <c r="I521" s="2" t="n"/>
@@ -38402,7 +38402,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดงทอง, แดงทอง, แดงเขียว, แดงเขียว</t>
         </is>
       </c>
       <c r="I522" s="2" t="n"/>
@@ -38458,7 +38458,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ครีม, สีครีม</t>
         </is>
       </c>
       <c r="I524" s="2" t="n"/>
@@ -38486,7 +38486,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>yellow</t>
+          <t>สีเหลือง, เหลือง</t>
         </is>
       </c>
       <c r="I525" s="2" t="n"/>
@@ -38514,7 +38514,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>สีทอง, สีทอง</t>
         </is>
       </c>
       <c r="I526" s="2" t="n"/>
@@ -38738,7 +38738,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>yellow</t>
+          <t>เหลือง, เหลือง, แดง, แดง</t>
         </is>
       </c>
       <c r="I534" s="2" t="n"/>
@@ -38766,7 +38766,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดง, แดง</t>
         </is>
       </c>
       <c r="I535" s="2" t="n"/>
@@ -38794,7 +38794,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>เหลืองทอง, สีทอง</t>
         </is>
       </c>
       <c r="I536" s="2" t="n"/>
@@ -38822,7 +38822,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดงเขียว, เขียวแดง</t>
         </is>
       </c>
       <c r="I537" s="2" t="n"/>
@@ -38906,7 +38906,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t>สีเงิน, เงิน</t>
         </is>
       </c>
       <c r="I540" s="2" t="n"/>
@@ -38934,7 +38934,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>เขียวอ่อน, เขียวอ่อน</t>
         </is>
       </c>
       <c r="I541" s="2" t="n"/>
@@ -38990,7 +38990,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดง, แดง</t>
         </is>
       </c>
       <c r="I543" s="2" t="n"/>
@@ -39154,7 +39154,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดง, แดง</t>
         </is>
       </c>
       <c r="I548" s="2" t="n"/>
@@ -39188,7 +39188,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>สีแดง, สีแดง</t>
         </is>
       </c>
       <c r="I549" s="2" t="n"/>
@@ -39318,7 +39318,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ทอง, ทอง</t>
         </is>
       </c>
       <c r="I553" s="2" t="n"/>
@@ -39380,7 +39380,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>ชมพู, ชมพู</t>
         </is>
       </c>
       <c r="I555" s="2" t="n"/>
@@ -39414,7 +39414,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t>เงิน, เงิน</t>
         </is>
       </c>
       <c r="I556" s="2" t="n"/>
@@ -39516,7 +39516,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>ฟ้า, เขียวอมฟ้า</t>
         </is>
       </c>
       <c r="I559" s="2" t="n"/>
@@ -39584,7 +39584,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>ชมพู, แดง</t>
         </is>
       </c>
       <c r="I561" s="2" t="n"/>
@@ -39618,7 +39618,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ทอง, เขียวเข้ม</t>
         </is>
       </c>
       <c r="I562" s="2" t="n"/>
@@ -39754,7 +39754,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ทอง, แดง</t>
         </is>
       </c>
       <c r="I566" s="2" t="n"/>
@@ -39788,7 +39788,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>แดง, แดง</t>
         </is>
       </c>
       <c r="I567" s="2" t="n"/>
@@ -39822,7 +39822,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>ขาว, ขาว</t>
         </is>
       </c>
       <c r="I568" s="2" t="n"/>
@@ -39924,7 +39924,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ทอง, เขียวเข้ม</t>
         </is>
       </c>
       <c r="I571" s="2" t="n"/>
@@ -40065,7 +40065,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>ชมพู, ชมพู</t>
         </is>
       </c>
       <c r="I575" s="2" t="n"/>
@@ -40365,7 +40365,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ทอง, สีน้ำตาลทอง</t>
         </is>
       </c>
       <c r="I584" s="2" t="n"/>
@@ -40529,7 +40529,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>ฟ้า, ทอง</t>
         </is>
       </c>
       <c r="I589" s="2" t="n"/>
@@ -40859,7 +40859,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ทอง, ทอง</t>
         </is>
       </c>
       <c r="I600" s="2" t="n"/>
@@ -40893,7 +40893,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>ชมพูอ่อน, ชมพูอ่อน</t>
         </is>
       </c>
       <c r="I601" s="2" t="n"/>
@@ -40961,7 +40961,7 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>ชมพูอ่อน, ชมพูอ่อน</t>
         </is>
       </c>
       <c r="I603" s="2" t="n"/>
@@ -41063,7 +41063,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t>สีเงิน, ทอง</t>
         </is>
       </c>
       <c r="I606" s="2" t="n"/>
@@ -41261,7 +41261,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>สีทอง, ทอง</t>
         </is>
       </c>
       <c r="I612" s="2" t="n"/>
@@ -41384,7 +41384,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>ทอง, ทอง</t>
         </is>
       </c>
       <c r="I616" s="2" t="n"/>
@@ -42095,7 +42095,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>สีเงิน, เงิน</t>
         </is>
       </c>
       <c r="I636" s="2" t="n"/>

--- a/catalog/product_worksheet.xlsx
+++ b/catalog/product_worksheet.xlsx
@@ -10,7 +10,7 @@
     <sheet name="products" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'products'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'products'!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20969,7 +20969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J830"/>
+  <dimension ref="A1:K830"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -20981,7 +20981,8 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21032,6 +21033,11 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>จำนวนต่อแพ็ค</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>หมายเหตุ — พนักงานกรอกเพิ่ม</t>
         </is>
       </c>
@@ -21715,7 +21721,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n"/>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 03013-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -21754,7 +21760,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n"/>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 02013-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -21861,7 +21867,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n"/>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 02012-1, 03012-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -21900,7 +21906,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n"/>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 01212-1, 03012-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -21939,7 +21945,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n"/>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 01212-1, 02012-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -22590,7 +22596,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n"/>
-      <c r="J46" s="3" t="inlineStr">
+      <c r="K46" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 12015-1/D — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -22799,7 +22805,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n"/>
-      <c r="J52" s="3" t="inlineStr">
+      <c r="K52" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 12015-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -23484,7 +23490,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n"/>
-      <c r="J72" s="3" t="inlineStr">
+      <c r="K72" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 07021-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -23523,7 +23529,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n"/>
-      <c r="J73" s="3" t="inlineStr">
+      <c r="K73" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 05021-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -23562,7 +23568,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n"/>
-      <c r="J74" s="3" t="inlineStr">
+      <c r="K74" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 05031-6, 06031-6, 07031-6 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -23601,7 +23607,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n"/>
-      <c r="J75" s="3" t="inlineStr">
+      <c r="K75" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 04031-6, 06031-6, 07031-6 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -23640,7 +23646,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n"/>
-      <c r="J76" s="3" t="inlineStr">
+      <c r="K76" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 04031-6, 05031-6, 07031-6 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -23679,7 +23685,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n"/>
-      <c r="J77" s="3" t="inlineStr">
+      <c r="K77" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 04031-6, 05031-6, 06031-6 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -23718,7 +23724,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n"/>
-      <c r="J78" s="3" t="inlineStr">
+      <c r="K78" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 05031-1, 06031-1, 07031-1, 08031-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -23757,7 +23763,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n"/>
-      <c r="J79" s="3" t="inlineStr">
+      <c r="K79" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 04031-1, 06031-1, 07031-1, 08031-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -23796,7 +23802,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n"/>
-      <c r="J80" s="3" t="inlineStr">
+      <c r="K80" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 04031-1, 05031-1, 07031-1, 08031-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -23835,7 +23841,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n"/>
-      <c r="J81" s="3" t="inlineStr">
+      <c r="K81" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 04031-1, 05031-1, 06031-1, 08031-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -23874,7 +23880,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n"/>
-      <c r="J82" s="3" t="inlineStr">
+      <c r="K82" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 04031-1, 05031-1, 06031-1, 07031-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -23913,7 +23919,7 @@
         </is>
       </c>
       <c r="I83" s="2" t="n"/>
-      <c r="J83" s="3" t="inlineStr">
+      <c r="K83" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 06092-1, 07092-1, 08092-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -23952,7 +23958,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n"/>
-      <c r="J84" s="3" t="inlineStr">
+      <c r="K84" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 05092-1, 07092-1, 08092-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -23991,7 +23997,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n"/>
-      <c r="J85" s="3" t="inlineStr">
+      <c r="K85" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 05092-1, 06092-1, 08092-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -24030,7 +24036,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n"/>
-      <c r="J86" s="3" t="inlineStr">
+      <c r="K86" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 05092-1, 06092-1, 07092-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -24069,7 +24075,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n"/>
-      <c r="J87" s="3" t="inlineStr">
+      <c r="K87" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 05032-1, 06032-1, 07032-1, 08032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -24108,7 +24114,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="n"/>
-      <c r="J88" s="3" t="inlineStr">
+      <c r="K88" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 04032-1, 06032-1, 07032-1, 08032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -24147,7 +24153,7 @@
         </is>
       </c>
       <c r="I89" s="2" t="n"/>
-      <c r="J89" s="3" t="inlineStr">
+      <c r="K89" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 04032-1, 05032-1, 07032-1, 08032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -24186,7 +24192,7 @@
         </is>
       </c>
       <c r="I90" s="2" t="n"/>
-      <c r="J90" s="3" t="inlineStr">
+      <c r="K90" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 04032-1, 05032-1, 06032-1, 08032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -24225,7 +24231,7 @@
         </is>
       </c>
       <c r="I91" s="2" t="n"/>
-      <c r="J91" s="3" t="inlineStr">
+      <c r="K91" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 04032-1, 05032-1, 06032-1, 07032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -24298,7 +24304,7 @@
         </is>
       </c>
       <c r="I93" s="2" t="n"/>
-      <c r="J93" s="3" t="inlineStr">
+      <c r="K93" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 26022-3, 27022-3, 28022-3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -24337,7 +24343,7 @@
         </is>
       </c>
       <c r="I94" s="2" t="n"/>
-      <c r="J94" s="3" t="inlineStr">
+      <c r="K94" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 25022-3, 27022-3, 28022-3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -24376,7 +24382,7 @@
         </is>
       </c>
       <c r="I95" s="2" t="n"/>
-      <c r="J95" s="3" t="inlineStr">
+      <c r="K95" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 25022-3, 26022-3, 28022-3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -24415,7 +24421,7 @@
         </is>
       </c>
       <c r="I96" s="2" t="n"/>
-      <c r="J96" s="3" t="inlineStr">
+      <c r="K96" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 25022-3, 26022-3, 27022-3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -24454,7 +24460,7 @@
         </is>
       </c>
       <c r="I97" s="2" t="n"/>
-      <c r="J97" s="3" t="inlineStr">
+      <c r="K97" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 05032-6, 06032-6, 07032-6 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -24493,7 +24499,7 @@
         </is>
       </c>
       <c r="I98" s="2" t="n"/>
-      <c r="J98" s="3" t="inlineStr">
+      <c r="K98" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 04032-6, 06032-6, 07032-6 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -24532,7 +24538,7 @@
         </is>
       </c>
       <c r="I99" s="2" t="n"/>
-      <c r="J99" s="3" t="inlineStr">
+      <c r="K99" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 04032-6, 05032-6, 07032-6 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -24571,7 +24577,7 @@
         </is>
       </c>
       <c r="I100" s="2" t="n"/>
-      <c r="J100" s="3" t="inlineStr">
+      <c r="K100" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 04032-6, 05032-6, 06032-6 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -24610,7 +24616,7 @@
         </is>
       </c>
       <c r="I101" s="2" t="n"/>
-      <c r="J101" s="3" t="inlineStr">
+      <c r="K101" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 87032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -24649,7 +24655,7 @@
         </is>
       </c>
       <c r="I102" s="2" t="n"/>
-      <c r="J102" s="3" t="inlineStr">
+      <c r="K102" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 86032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -24688,7 +24694,7 @@
         </is>
       </c>
       <c r="I103" s="2" t="n"/>
-      <c r="J103" s="3" t="inlineStr">
+      <c r="K103" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 87031-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -24727,7 +24733,7 @@
         </is>
       </c>
       <c r="I104" s="2" t="n"/>
-      <c r="J104" s="3" t="inlineStr">
+      <c r="K104" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 86031-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -24800,7 +24806,7 @@
         </is>
       </c>
       <c r="I106" s="2" t="n"/>
-      <c r="J106" s="3" t="inlineStr">
+      <c r="K106" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 01235-1, 01535-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -24839,7 +24845,7 @@
         </is>
       </c>
       <c r="I107" s="2" t="n"/>
-      <c r="J107" s="3" t="inlineStr">
+      <c r="K107" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 01035-1, 01535-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -24878,7 +24884,7 @@
         </is>
       </c>
       <c r="I108" s="2" t="n"/>
-      <c r="J108" s="3" t="inlineStr">
+      <c r="K108" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 01035-1, 01235-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -25024,7 +25030,7 @@
         </is>
       </c>
       <c r="I112" s="2" t="n"/>
-      <c r="J112" s="3" t="inlineStr">
+      <c r="K112" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 07012-2, 08012-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -25063,7 +25069,7 @@
         </is>
       </c>
       <c r="I113" s="2" t="n"/>
-      <c r="J113" s="3" t="inlineStr">
+      <c r="K113" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 04072-1, 08012-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -25102,7 +25108,7 @@
         </is>
       </c>
       <c r="I114" s="2" t="n"/>
-      <c r="J114" s="3" t="inlineStr">
+      <c r="K114" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 04072-1, 07012-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -25135,7 +25141,7 @@
         </is>
       </c>
       <c r="I115" s="2" t="n"/>
-      <c r="J115" s="3" t="inlineStr">
+      <c r="K115" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 07512-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -25174,7 +25180,7 @@
         </is>
       </c>
       <c r="I116" s="2" t="n"/>
-      <c r="J116" s="3" t="inlineStr">
+      <c r="K116" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 05572-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -25247,7 +25253,7 @@
         </is>
       </c>
       <c r="I118" s="2" t="n"/>
-      <c r="J118" s="3" t="inlineStr">
+      <c r="K118" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 41592-1, 42092-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -25286,7 +25292,7 @@
         </is>
       </c>
       <c r="I119" s="2" t="n"/>
-      <c r="J119" s="3" t="inlineStr">
+      <c r="K119" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 41092-1, 42092-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -25325,7 +25331,7 @@
         </is>
       </c>
       <c r="I120" s="2" t="n"/>
-      <c r="J120" s="3" t="inlineStr">
+      <c r="K120" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 41092-1, 41592-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -25398,7 +25404,7 @@
         </is>
       </c>
       <c r="I122" s="2" t="n"/>
-      <c r="J122" s="3" t="inlineStr">
+      <c r="K122" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 26022-2, 27022-2, 28022-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -25437,7 +25443,7 @@
         </is>
       </c>
       <c r="I123" s="2" t="n"/>
-      <c r="J123" s="3" t="inlineStr">
+      <c r="K123" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 25022-2, 27022-2, 28022-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -25476,7 +25482,7 @@
         </is>
       </c>
       <c r="I124" s="2" t="n"/>
-      <c r="J124" s="3" t="inlineStr">
+      <c r="K124" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 25022-2, 26022-2, 28022-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -25515,7 +25521,7 @@
         </is>
       </c>
       <c r="I125" s="2" t="n"/>
-      <c r="J125" s="3" t="inlineStr">
+      <c r="K125" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 25022-2, 26022-2, 27022-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -25554,7 +25560,7 @@
         </is>
       </c>
       <c r="I126" s="2" t="n"/>
-      <c r="J126" s="3" t="inlineStr">
+      <c r="K126" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 08012-3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -25593,7 +25599,7 @@
         </is>
       </c>
       <c r="I127" s="2" t="n"/>
-      <c r="J127" s="3" t="inlineStr">
+      <c r="K127" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 06012-3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -25766,7 +25772,7 @@
         </is>
       </c>
       <c r="I132" s="2" t="n"/>
-      <c r="J132" s="3" t="inlineStr">
+      <c r="K132" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 45032-1, 46032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -25805,7 +25811,7 @@
         </is>
       </c>
       <c r="I133" s="2" t="n"/>
-      <c r="J133" s="3" t="inlineStr">
+      <c r="K133" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 44032-1, 46032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -25844,7 +25850,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n"/>
-      <c r="J134" s="3" t="inlineStr">
+      <c r="K134" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 44032-1, 45032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -25883,7 +25889,7 @@
         </is>
       </c>
       <c r="I135" s="2" t="n"/>
-      <c r="J135" s="3" t="inlineStr">
+      <c r="K135" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 48032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -25922,7 +25928,7 @@
         </is>
       </c>
       <c r="I136" s="2" t="n"/>
-      <c r="J136" s="3" t="inlineStr">
+      <c r="K136" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 47032-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -25995,7 +26001,7 @@
         </is>
       </c>
       <c r="I138" s="2" t="n"/>
-      <c r="J138" s="3" t="inlineStr">
+      <c r="K138" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 37072-1, 34072-1, 36072-1, 38072-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -26034,7 +26040,7 @@
         </is>
       </c>
       <c r="I139" s="2" t="n"/>
-      <c r="J139" s="3" t="inlineStr">
+      <c r="K139" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 35072-1, 34072-1, 36072-1, 38072-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -26073,7 +26079,7 @@
         </is>
       </c>
       <c r="I140" s="2" t="n"/>
-      <c r="J140" s="3" t="inlineStr">
+      <c r="K140" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 38092-5 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -26112,7 +26118,7 @@
         </is>
       </c>
       <c r="I141" s="2" t="n"/>
-      <c r="J141" s="3" t="inlineStr">
+      <c r="K141" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 36092-4 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -26151,7 +26157,7 @@
         </is>
       </c>
       <c r="I142" s="2" t="n"/>
-      <c r="J142" s="3" t="inlineStr">
+      <c r="K142" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 36031-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -26190,7 +26196,7 @@
         </is>
       </c>
       <c r="I143" s="2" t="n"/>
-      <c r="J143" s="3" t="inlineStr">
+      <c r="K143" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 35031-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -26229,7 +26235,7 @@
         </is>
       </c>
       <c r="I144" s="2" t="n"/>
-      <c r="J144" s="3" t="inlineStr">
+      <c r="K144" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 35072-1, 37072-1, 36072-1, 38072-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -26268,7 +26274,7 @@
         </is>
       </c>
       <c r="I145" s="2" t="n"/>
-      <c r="J145" s="3" t="inlineStr">
+      <c r="K145" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 35072-1, 37072-1, 34072-1, 38072-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -26307,7 +26313,7 @@
         </is>
       </c>
       <c r="I146" s="2" t="n"/>
-      <c r="J146" s="3" t="inlineStr">
+      <c r="K146" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 35072-1, 37072-1, 34072-1, 36072-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -27026,7 +27032,7 @@
         </is>
       </c>
       <c r="I167" s="2" t="n"/>
-      <c r="J167" s="3" t="inlineStr">
+      <c r="K167" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 56614-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -27167,7 +27173,7 @@
         </is>
       </c>
       <c r="I171" s="2" t="n"/>
-      <c r="J171" s="3" t="inlineStr">
+      <c r="K171" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 56614-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -27240,7 +27246,7 @@
         </is>
       </c>
       <c r="I173" s="2" t="n"/>
-      <c r="J173" s="3" t="inlineStr">
+      <c r="K173" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 56718-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -27381,7 +27387,7 @@
         </is>
       </c>
       <c r="I177" s="2" t="n"/>
-      <c r="J177" s="3" t="inlineStr">
+      <c r="K177" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 53618-5 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -27488,7 +27494,7 @@
         </is>
       </c>
       <c r="I180" s="2" t="n"/>
-      <c r="J180" s="3" t="inlineStr">
+      <c r="K180" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 55820-1, 55924-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -27527,7 +27533,7 @@
         </is>
       </c>
       <c r="I181" s="2" t="n"/>
-      <c r="J181" s="3" t="inlineStr">
+      <c r="K181" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 56918-1, 55924-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -27566,7 +27572,7 @@
         </is>
       </c>
       <c r="I182" s="2" t="n"/>
-      <c r="J182" s="3" t="inlineStr">
+      <c r="K182" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 56918-1, 55820-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -27871,7 +27877,7 @@
         </is>
       </c>
       <c r="I191" s="2" t="n"/>
-      <c r="J191" s="3" t="inlineStr">
+      <c r="K191" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 71016-1/DR/66 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -27932,7 +27938,7 @@
         </is>
       </c>
       <c r="I193" s="2" t="n"/>
-      <c r="J193" s="3" t="inlineStr">
+      <c r="K193" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 71016-1/DG/66 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -28021,7 +28027,7 @@
         </is>
       </c>
       <c r="I196" s="2" t="n"/>
-      <c r="J196" s="3" t="inlineStr">
+      <c r="K196" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 74026-1/D2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -28082,7 +28088,7 @@
         </is>
       </c>
       <c r="I198" s="2" t="n"/>
-      <c r="J198" s="3" t="inlineStr">
+      <c r="K198" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 74026-1/D1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -28171,7 +28177,7 @@
         </is>
       </c>
       <c r="I201" s="2" t="n"/>
-      <c r="J201" s="3" t="inlineStr">
+      <c r="K201" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 60801-1, 60959-1, 61001-1, 60851-1, 61002-1, 60852-1, 60850-6, 61004-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -28204,7 +28210,7 @@
         </is>
       </c>
       <c r="I202" s="2" t="n"/>
-      <c r="J202" s="3" t="inlineStr">
+      <c r="K202" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 60850-2, 60959-1, 61001-1, 60851-1, 61002-1, 60852-1, 60850-6, 61004-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -28237,7 +28243,7 @@
         </is>
       </c>
       <c r="I203" s="2" t="n"/>
-      <c r="J203" s="3" t="inlineStr">
+      <c r="K203" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 60850-2, 60801-1, 61001-1, 60851-1, 61002-1, 60852-1, 60850-6, 61004-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -28270,7 +28276,7 @@
         </is>
       </c>
       <c r="I204" s="2" t="n"/>
-      <c r="J204" s="3" t="inlineStr">
+      <c r="K204" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 60850-2, 60801-1, 60959-1, 60851-1, 61002-1, 60852-1, 60850-6, 61004-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -28303,7 +28309,7 @@
         </is>
       </c>
       <c r="I205" s="2" t="n"/>
-      <c r="J205" s="3" t="inlineStr">
+      <c r="K205" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 60850-2, 60801-1, 60959-1, 61001-1, 61002-1, 60852-1, 60850-6, 61004-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -28336,7 +28342,7 @@
         </is>
       </c>
       <c r="I206" s="2" t="n"/>
-      <c r="J206" s="3" t="inlineStr">
+      <c r="K206" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 60850-2, 60801-1, 60959-1, 61001-1, 60851-1, 60852-1, 60850-6, 61004-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -28369,7 +28375,7 @@
         </is>
       </c>
       <c r="I207" s="2" t="n"/>
-      <c r="J207" s="3" t="inlineStr">
+      <c r="K207" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 60850-2, 60801-1, 60959-1, 61001-1, 60851-1, 61002-1, 60850-6, 61004-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -28402,7 +28408,7 @@
         </is>
       </c>
       <c r="I208" s="2" t="n"/>
-      <c r="J208" s="3" t="inlineStr">
+      <c r="K208" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 60850-2, 60801-1, 60959-1, 61001-1, 60851-1, 61002-1, 60852-1, 61004-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -28435,7 +28441,7 @@
         </is>
       </c>
       <c r="I209" s="2" t="n"/>
-      <c r="J209" s="3" t="inlineStr">
+      <c r="K209" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 61056-1, 61256-1, 61055-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -28468,7 +28474,7 @@
         </is>
       </c>
       <c r="I210" s="2" t="n"/>
-      <c r="J210" s="3" t="inlineStr">
+      <c r="K210" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 61202-1, 61205-1, 61255-3, 61059-1, 61255-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -28501,7 +28507,7 @@
         </is>
       </c>
       <c r="I211" s="2" t="n"/>
-      <c r="J211" s="3" t="inlineStr">
+      <c r="K211" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 61052-1, 61205-1, 61255-3, 61059-1, 61255-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -28534,7 +28540,7 @@
         </is>
       </c>
       <c r="I212" s="2" t="n"/>
-      <c r="J212" s="3" t="inlineStr">
+      <c r="K212" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 61052-1, 61202-1, 61255-3, 61059-1, 61255-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -28567,7 +28573,7 @@
         </is>
       </c>
       <c r="I213" s="2" t="n"/>
-      <c r="J213" s="3" t="inlineStr">
+      <c r="K213" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 61058-1, 61256-1, 61055-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -28600,7 +28606,7 @@
         </is>
       </c>
       <c r="I214" s="2" t="n"/>
-      <c r="J214" s="3" t="inlineStr">
+      <c r="K214" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 61052-1, 61202-1, 61205-1, 61059-1, 61255-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -28633,7 +28639,7 @@
         </is>
       </c>
       <c r="I215" s="2" t="n"/>
-      <c r="J215" s="3" t="inlineStr">
+      <c r="K215" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 61052-1, 61202-1, 61205-1, 61255-3, 61255-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -28666,7 +28672,7 @@
         </is>
       </c>
       <c r="I216" s="2" t="n"/>
-      <c r="J216" s="3" t="inlineStr">
+      <c r="K216" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 60850-2, 60801-1, 60959-1, 61001-1, 60851-1, 61002-1, 60852-1, 60850-6 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -28699,7 +28705,7 @@
         </is>
       </c>
       <c r="I217" s="2" t="n"/>
-      <c r="J217" s="3" t="inlineStr">
+      <c r="K217" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 61058-1, 61056-1, 61055-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -28732,7 +28738,7 @@
         </is>
       </c>
       <c r="I218" s="2" t="n"/>
-      <c r="J218" s="3" t="inlineStr">
+      <c r="K218" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 61058-1, 61056-1, 61256-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -28765,7 +28771,7 @@
         </is>
       </c>
       <c r="I219" s="2" t="n"/>
-      <c r="J219" s="3" t="inlineStr">
+      <c r="K219" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 61052-1, 61202-1, 61205-1, 61255-3, 61059-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -29013,7 +29019,7 @@
         </is>
       </c>
       <c r="I226" s="2" t="n"/>
-      <c r="J226" s="3" t="inlineStr">
+      <c r="K226" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 70912-3/D1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -29052,7 +29058,7 @@
         </is>
       </c>
       <c r="I227" s="2" t="n"/>
-      <c r="J227" s="3" t="inlineStr">
+      <c r="K227" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 70912-4/D — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -29255,7 +29261,7 @@
         </is>
       </c>
       <c r="I233" s="2" t="n"/>
-      <c r="J233" s="3" t="inlineStr">
+      <c r="K233" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 70912-4/D3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -29294,7 +29300,7 @@
         </is>
       </c>
       <c r="I234" s="2" t="n"/>
-      <c r="J234" s="3" t="inlineStr">
+      <c r="K234" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 70612-2/D2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -29367,7 +29373,7 @@
         </is>
       </c>
       <c r="I236" s="2" t="n"/>
-      <c r="J236" s="3" t="inlineStr">
+      <c r="K236" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 70023-4 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -29406,7 +29412,7 @@
         </is>
       </c>
       <c r="I237" s="2" t="n"/>
-      <c r="J237" s="3" t="inlineStr">
+      <c r="K237" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 70412-3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -30311,7 +30317,7 @@
         </is>
       </c>
       <c r="I264" s="2" t="n"/>
-      <c r="J264" s="3" t="inlineStr">
+      <c r="K264" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 039-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -30350,7 +30356,7 @@
         </is>
       </c>
       <c r="I265" s="2" t="n"/>
-      <c r="J265" s="3" t="inlineStr">
+      <c r="K265" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 017-08 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -30983,7 +30989,7 @@
         </is>
       </c>
       <c r="I284" s="2" t="n"/>
-      <c r="J284" s="3" t="inlineStr">
+      <c r="K284" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 053-06 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -31022,7 +31028,7 @@
         </is>
       </c>
       <c r="I285" s="2" t="n"/>
-      <c r="J285" s="3" t="inlineStr">
+      <c r="K285" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 059-07 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -31743,7 +31749,7 @@
         </is>
       </c>
       <c r="I308" s="2" t="n"/>
-      <c r="J308" s="3" t="inlineStr">
+      <c r="K308" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 107-03, 107-04 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -31832,7 +31838,7 @@
         </is>
       </c>
       <c r="I311" s="2" t="n"/>
-      <c r="J311" s="3" t="inlineStr">
+      <c r="K311" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 107-02, 107-04 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -31865,7 +31871,7 @@
         </is>
       </c>
       <c r="I312" s="2" t="n"/>
-      <c r="J312" s="3" t="inlineStr">
+      <c r="K312" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 107-02, 107-03 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -32350,7 +32356,7 @@
         </is>
       </c>
       <c r="I327" s="2" t="n"/>
-      <c r="J327" s="3" t="inlineStr">
+      <c r="K327" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 048-02, 073-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -32389,7 +32395,7 @@
         </is>
       </c>
       <c r="I328" s="2" t="n"/>
-      <c r="J328" s="3" t="inlineStr">
+      <c r="K328" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 047-02, 073-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -32428,7 +32434,7 @@
         </is>
       </c>
       <c r="I329" s="2" t="n"/>
-      <c r="J329" s="3" t="inlineStr">
+      <c r="K329" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 047-02, 048-02 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -32569,7 +32575,7 @@
         </is>
       </c>
       <c r="I333" s="2" t="n"/>
-      <c r="J333" s="3" t="inlineStr">
+      <c r="K333" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 90251-1, 90252-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -32608,7 +32614,7 @@
         </is>
       </c>
       <c r="I334" s="2" t="n"/>
-      <c r="J334" s="3" t="inlineStr">
+      <c r="K334" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 90253-3, 90252-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -32647,7 +32653,7 @@
         </is>
       </c>
       <c r="I335" s="2" t="n"/>
-      <c r="J335" s="3" t="inlineStr">
+      <c r="K335" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 90253-3, 90251-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -32686,7 +32692,7 @@
         </is>
       </c>
       <c r="I336" s="2" t="n"/>
-      <c r="J336" s="3" t="inlineStr">
+      <c r="K336" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 90232-8 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -32725,7 +32731,7 @@
         </is>
       </c>
       <c r="I337" s="2" t="n"/>
-      <c r="J337" s="3" t="inlineStr">
+      <c r="K337" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 90249-3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -33522,7 +33528,7 @@
         </is>
       </c>
       <c r="I361" s="2" t="n"/>
-      <c r="J361" s="3" t="inlineStr">
+      <c r="K361" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 90564-4 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -33555,7 +33561,7 @@
         </is>
       </c>
       <c r="I362" s="2" t="n"/>
-      <c r="J362" s="3" t="inlineStr">
+      <c r="K362" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 90577-3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -34776,7 +34782,7 @@
         </is>
       </c>
       <c r="I405" s="2" t="n"/>
-      <c r="J405" s="3" t="inlineStr">
+      <c r="K405" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 6121-02 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -34815,7 +34821,7 @@
         </is>
       </c>
       <c r="I406" s="2" t="n"/>
-      <c r="J406" s="3" t="inlineStr">
+      <c r="K406" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 6121-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -34904,7 +34910,7 @@
         </is>
       </c>
       <c r="I409" s="2" t="n"/>
-      <c r="J409" s="3" t="inlineStr">
+      <c r="K409" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 90767-3, 90773-1, 90774-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -34937,7 +34943,7 @@
         </is>
       </c>
       <c r="I410" s="2" t="n"/>
-      <c r="J410" s="3" t="inlineStr">
+      <c r="K410" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 90772-1, 90773-1, 90774-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -34976,7 +34982,7 @@
         </is>
       </c>
       <c r="I411" s="2" t="n"/>
-      <c r="J411" s="3" t="inlineStr">
+      <c r="K411" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 6704-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -35015,7 +35021,7 @@
         </is>
       </c>
       <c r="I412" s="2" t="n"/>
-      <c r="J412" s="3" t="inlineStr">
+      <c r="K412" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 6703-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -35104,7 +35110,7 @@
         </is>
       </c>
       <c r="I415" s="2" t="n"/>
-      <c r="J415" s="3" t="inlineStr">
+      <c r="K415" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 90772-1, 90767-3, 90774-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -35137,7 +35143,7 @@
         </is>
       </c>
       <c r="I416" s="2" t="n"/>
-      <c r="J416" s="3" t="inlineStr">
+      <c r="K416" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 90772-1, 90767-3, 90773-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -35204,7 +35210,7 @@
         </is>
       </c>
       <c r="I418" s="2" t="n"/>
-      <c r="J418" s="3" t="inlineStr">
+      <c r="K418" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 6753-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -35243,7 +35249,7 @@
         </is>
       </c>
       <c r="I419" s="2" t="n"/>
-      <c r="J419" s="3" t="inlineStr">
+      <c r="K419" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 6754-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -35282,7 +35288,7 @@
         </is>
       </c>
       <c r="I420" s="2" t="n"/>
-      <c r="J420" s="3" t="inlineStr">
+      <c r="K420" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 6120-02 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -35321,7 +35327,7 @@
         </is>
       </c>
       <c r="I421" s="2" t="n"/>
-      <c r="J421" s="3" t="inlineStr">
+      <c r="K421" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 6120-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -35726,7 +35732,7 @@
         </is>
       </c>
       <c r="I434" s="2" t="n"/>
-      <c r="J434" s="3" t="inlineStr">
+      <c r="K434" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 6384-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -35765,7 +35771,7 @@
         </is>
       </c>
       <c r="I435" s="2" t="n"/>
-      <c r="J435" s="3" t="inlineStr">
+      <c r="K435" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 6730-02 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -35865,7 +35871,7 @@
         </is>
       </c>
       <c r="I438" s="2" t="n"/>
-      <c r="J438" s="3" t="inlineStr">
+      <c r="K438" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 90663-18 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -35909,7 +35915,7 @@
         </is>
       </c>
       <c r="I439" s="2" t="n"/>
-      <c r="J439" s="3" t="inlineStr">
+      <c r="K439" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 90634-8 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -36366,7 +36372,7 @@
         </is>
       </c>
       <c r="I453" s="2" t="n"/>
-      <c r="J453" s="3" t="inlineStr">
+      <c r="K453" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 90707-2, 90755-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -36405,7 +36411,7 @@
         </is>
       </c>
       <c r="I454" s="2" t="n"/>
-      <c r="J454" s="3" t="inlineStr">
+      <c r="K454" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 90754-3, 90755-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -36444,7 +36450,7 @@
         </is>
       </c>
       <c r="I455" s="2" t="n"/>
-      <c r="J455" s="3" t="inlineStr">
+      <c r="K455" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 90754-3, 90707-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -36961,7 +36967,7 @@
         </is>
       </c>
       <c r="I472" s="2" t="n"/>
-      <c r="J472" s="3" t="inlineStr">
+      <c r="K472" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 5713-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -36994,7 +37000,7 @@
         </is>
       </c>
       <c r="I473" s="2" t="n"/>
-      <c r="J473" s="3" t="inlineStr">
+      <c r="K473" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 5702-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -37139,7 +37145,7 @@
         </is>
       </c>
       <c r="I478" s="2" t="n"/>
-      <c r="J478" s="3" t="inlineStr">
+      <c r="K478" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 72033-1, 73033-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -37172,7 +37178,7 @@
         </is>
       </c>
       <c r="I479" s="2" t="n"/>
-      <c r="J479" s="3" t="inlineStr">
+      <c r="K479" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 71533-1, 73033-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -37205,7 +37211,7 @@
         </is>
       </c>
       <c r="I480" s="2" t="n"/>
-      <c r="J480" s="3" t="inlineStr">
+      <c r="K480" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 71533-1, 72033-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -37686,7 +37692,7 @@
         </is>
       </c>
       <c r="I497" s="2" t="n"/>
-      <c r="J497" s="3" t="inlineStr">
+      <c r="K497" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 5871-02 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -37719,7 +37725,7 @@
         </is>
       </c>
       <c r="I498" s="2" t="n"/>
-      <c r="J498" s="3" t="inlineStr">
+      <c r="K498" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 5871-01 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -37920,7 +37926,7 @@
         </is>
       </c>
       <c r="I505" s="2" t="n"/>
-      <c r="J505" s="3" t="inlineStr">
+      <c r="K505" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 5890-03 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -37953,7 +37959,7 @@
         </is>
       </c>
       <c r="I506" s="2" t="n"/>
-      <c r="J506" s="3" t="inlineStr">
+      <c r="K506" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 5871-03 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -40741,7 +40747,7 @@
         </is>
       </c>
       <c r="I596" s="2" t="n"/>
-      <c r="J596" s="3" t="inlineStr">
+      <c r="K596" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 90586-4 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -40774,7 +40780,7 @@
         </is>
       </c>
       <c r="I597" s="2" t="n"/>
-      <c r="J597" s="3" t="inlineStr">
+      <c r="K597" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 90586-3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -41416,7 +41422,7 @@
         </is>
       </c>
       <c r="I617" s="2" t="n"/>
-      <c r="J617" s="3" t="inlineStr">
+      <c r="K617" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 6124-02 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -41449,7 +41455,7 @@
         </is>
       </c>
       <c r="I618" s="2" t="n"/>
-      <c r="J618" s="3" t="inlineStr">
+      <c r="K618" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 6117-07 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -41550,7 +41556,7 @@
         </is>
       </c>
       <c r="I621" s="2" t="n"/>
-      <c r="J621" s="3" t="inlineStr">
+      <c r="K621" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 6114-05, 6191-03 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -41589,7 +41595,7 @@
         </is>
       </c>
       <c r="I622" s="2" t="n"/>
-      <c r="J622" s="3" t="inlineStr">
+      <c r="K622" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 6111-02, 6191-03 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -41628,7 +41634,7 @@
         </is>
       </c>
       <c r="I623" s="2" t="n"/>
-      <c r="J623" s="3" t="inlineStr">
+      <c r="K623" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 6111-02, 6114-05 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -41667,7 +41673,7 @@
         </is>
       </c>
       <c r="I624" s="2" t="n"/>
-      <c r="J624" s="3" t="inlineStr">
+      <c r="K624" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 90698-5 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -41706,7 +41712,7 @@
         </is>
       </c>
       <c r="I625" s="2" t="n"/>
-      <c r="J625" s="3" t="inlineStr">
+      <c r="K625" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 90651-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -41881,7 +41887,7 @@
         </is>
       </c>
       <c r="I630" s="2" t="n"/>
-      <c r="J630" s="3" t="inlineStr">
+      <c r="K630" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 79015-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -41920,7 +41926,7 @@
         </is>
       </c>
       <c r="I631" s="2" t="n"/>
-      <c r="J631" s="3" t="inlineStr">
+      <c r="K631" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 76015-2 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -41993,7 +41999,7 @@
         </is>
       </c>
       <c r="I633" s="2" t="n"/>
-      <c r="J633" s="3" t="inlineStr">
+      <c r="K633" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 76015-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -42032,7 +42038,7 @@
         </is>
       </c>
       <c r="I634" s="2" t="n"/>
-      <c r="J634" s="3" t="inlineStr">
+      <c r="K634" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 79015-1 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -42127,7 +42133,7 @@
         </is>
       </c>
       <c r="I637" s="2" t="n"/>
-      <c r="J637" s="3" t="inlineStr">
+      <c r="K637" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 76015-3 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -42160,7 +42166,7 @@
         </is>
       </c>
       <c r="I638" s="2" t="n"/>
-      <c r="J638" s="3" t="inlineStr">
+      <c r="K638" s="3" t="inlineStr">
         <is>
           <t>รูปนี้ใช้ร่วมกับ 71015-5 — เช็ครหัสให้ตรงก่อนยืนยันสินค้าจริง</t>
         </is>
@@ -44180,7 +44186,7 @@
         </is>
       </c>
       <c r="F711" t="n">
-        <v>350</v>
+        <v>600</v>
       </c>
       <c r="G711" s="2" t="inlineStr"/>
       <c r="H711" s="2" t="inlineStr"/>
@@ -44236,7 +44242,7 @@
         </is>
       </c>
       <c r="F713" t="n">
-        <v>360</v>
+        <v>600</v>
       </c>
       <c r="G713" s="2" t="inlineStr"/>
       <c r="H713" s="2" t="inlineStr"/>
@@ -44264,7 +44270,7 @@
         </is>
       </c>
       <c r="F714" t="n">
-        <v>420</v>
+        <v>600</v>
       </c>
       <c r="G714" s="2" t="inlineStr"/>
       <c r="H714" s="2" t="inlineStr"/>
@@ -44292,7 +44298,7 @@
         </is>
       </c>
       <c r="F715" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="G715" s="2" t="inlineStr"/>
       <c r="H715" s="2" t="inlineStr"/>
@@ -44320,7 +44326,7 @@
         </is>
       </c>
       <c r="F716" t="n">
-        <v>410</v>
+        <v>750</v>
       </c>
       <c r="G716" s="2" t="inlineStr"/>
       <c r="H716" s="2" t="inlineStr"/>
@@ -44376,7 +44382,7 @@
         </is>
       </c>
       <c r="F718" t="n">
-        <v>360</v>
+        <v>600</v>
       </c>
       <c r="G718" s="2" t="inlineStr"/>
       <c r="H718" s="2" t="inlineStr"/>
@@ -47485,7 +47491,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
